--- a/docs/ux/mode-separation/UX_Mode_Separation_Discovery_Tracker.xlsx
+++ b/docs/ux/mode-separation/UX_Mode_Separation_Discovery_Tracker.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="1" r:id="R5fe3f358e7d94b53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline" sheetId="2" r:id="Rceea4208cbc14938"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prototype Results" sheetId="3" r:id="Rfe95b3ad612844a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" r:id="R4b7a8fc8868d4bce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="1" r:id="R774a744d470549b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline" sheetId="2" r:id="Rbb44d1dd6693470e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prototype Results" sheetId="3" r:id="R56055f288d6c4652"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="4" r:id="R29527a1ab12c4d62"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,31 +16,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
-    <x:numFmt numFmtId="200" formatCode="0"/>
+  <x:numFmts count="4">
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="201" formatCode="0.000"/>
-    <x:numFmt numFmtId="202" formatCode="yyyy-mm-dd"/>
+    <x:numFmt numFmtId="202" formatCode="0"/>
+    <x:numFmt numFmtId="203" formatCode="0.0%"/>
   </x:numFmts>
-  <x:fonts count="7">
+  <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="16"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FF1D1D1F"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF6B4E00"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
@@ -50,17 +34,12 @@
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:name val="Arial"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF6B4E00"/>
+      <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -74,64 +53,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFE8F2FF"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFF4CE"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="24">
+  <x:borders count="7">
     <x:border/>
-    <x:border/>
-    <x:border>
-      <x:bottom style="double">
-        <x:color rgb="FFA9CFFF"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:bottom style="double">
-        <x:color rgb="FFA9CFFF"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:bottom style="thin">
-        <x:color rgb="FFE5E5EA"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:top style="thin">
-        <x:color rgb="FFE5E5EA"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFE5E5EA"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:top style="thin">
-        <x:color rgb="FFE5E5EA"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:bottom style="thin">
-        <x:color rgb="FFE5E5EA"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:top style="thin">
-        <x:color rgb="FFE5E5EA"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFE5E5EA"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:top style="thin">
-        <x:color rgb="FFE5E5EA"/>
-      </x:top>
-    </x:border>
     <x:border>
       <x:left style="thin">
         <x:color rgb="FFF1C75B"/>
@@ -174,265 +101,135 @@
         <x:color rgb="FFF1C75B"/>
       </x:bottom>
     </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFF1C75B"/>
-      </x:left>
-      <x:top style="thin">
-        <x:color rgb="FFF1C75B"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:top style="thin">
-        <x:color rgb="FFF1C75B"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFF1C75B"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFF1C75B"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFF1C75B"/>
-      </x:left>
-      <x:bottom style="thin">
-        <x:color rgb="FFF1C75B"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:bottom style="thin">
-        <x:color rgb="FFF1C75B"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFF1C75B"/>
-      </x:right>
-      <x:bottom style="thin">
-        <x:color rgb="FFF1C75B"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:bottom style="double">
-        <x:color rgb="FF005FCC"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:bottom style="double">
-        <x:color rgb="FF005FCC"/>
-      </x:bottom>
-    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="92">
+  <x:cellXfs count="37">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="2">
+  <x:dxfs count="4">
     <x:dxf>
       <x:font>
-        <x:color rgb="FF16733C"/>
+        <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
         <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFDDF6E5"/>
+          <x:bgColor rgb="FFE3F5E8"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:font>
-        <x:color rgb="FFB42318"/>
+        <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
         <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFFE2E0"/>
+          <x:bgColor rgb="FFE3F5E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE3F5E8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF6B4E00"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF4CE"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -442,6 +239,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ScenariosTable" displayName="ScenariosTable" ref="A1:K6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:K6"/>
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="scenario_id"/>
     <x:tableColumn id="2" name="journey"/>
@@ -460,7 +258,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="BaselineTable" displayName="BaselineTable" ref="A1:V11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="BaselineResultsTable" displayName="BaselineResultsTable" ref="A1:V11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:V11"/>
   <x:tableColumns count="22">
     <x:tableColumn id="1" name="run_id"/>
     <x:tableColumn id="2" name="record_type"/>
@@ -486,6 +285,74 @@
     <x:tableColumn id="22" name="limitations"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PrototypeResultsTable" displayName="PrototypeResultsTable" ref="A1:V31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:V31"/>
+  <x:tableColumns count="22">
+    <x:tableColumn id="1" name="run_id"/>
+    <x:tableColumn id="2" name="record_type"/>
+    <x:tableColumn id="3" name="scenario_id"/>
+    <x:tableColumn id="4" name="variant"/>
+    <x:tableColumn id="5" name="environment"/>
+    <x:tableColumn id="6" name="viewport"/>
+    <x:tableColumn id="7" name="test_date"/>
+    <x:tableColumn id="8" name="operator"/>
+    <x:tableColumn id="9" name="method"/>
+    <x:tableColumn id="10" name="status"/>
+    <x:tableColumn id="11" name="elapsed_seconds"/>
+    <x:tableColumn id="12" name="click_count"/>
+    <x:tableColumn id="13" name="scroll_count"/>
+    <x:tableColumn id="14" name="key_count"/>
+    <x:tableColumn id="15" name="error_count"/>
+    <x:tableColumn id="16" name="recovery_count"/>
+    <x:tableColumn id="17" name="start_state"/>
+    <x:tableColumn id="18" name="end_state"/>
+    <x:tableColumn id="19" name="observation"/>
+    <x:tableColumn id="20" name="evidence"/>
+    <x:tableColumn id="21" name="human_participant_id"/>
+    <x:tableColumn id="22" name="limitations"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="BaselineOverviewTable" displayName="BaselineOverviewTable" ref="A3:C9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="3">
+    <x:tableColumn id="1" name="指標"/>
+    <x:tableColumn id="2" name="値"/>
+    <x:tableColumn id="3" name="説明"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="PrototypeOverviewTable" displayName="PrototypeOverviewTable" ref="A11:F17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="6">
+    <x:tableColumn id="1" name="案"/>
+    <x:tableColumn id="2" name="環境"/>
+    <x:tableColumn id="3" name="完了"/>
+    <x:tableColumn id="4" name="クリック"/>
+    <x:tableColumn id="5" name="スクロール"/>
+    <x:tableColumn id="6" name="自動操作秒"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="AnalysisScrollGateTable" displayName="AnalysisScrollGateTable" ref="A21:D25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="4">
+    <x:tableColumn id="1" name="案"/>
+    <x:tableColumn id="2" name="スクロール"/>
+    <x:tableColumn id="3" name="BASE比削減"/>
+    <x:tableColumn id="4" name="50%目標"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </x:table>
 </file>
 
@@ -684,233 +551,233 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="34" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="10" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="10" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="28" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="26" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="38" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="80" t="str">
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="3" t="str">
         <x:v>scenario_id</x:v>
       </x:c>
-      <x:c r="B1" s="80" t="str">
+      <x:c r="B1" s="3" t="str">
         <x:v>journey</x:v>
       </x:c>
-      <x:c r="C1" s="80" t="str">
+      <x:c r="C1" s="3" t="str">
         <x:v>goal</x:v>
       </x:c>
-      <x:c r="D1" s="80" t="str">
+      <x:c r="D1" s="3" t="str">
         <x:v>start_state</x:v>
       </x:c>
-      <x:c r="E1" s="80" t="str">
+      <x:c r="E1" s="3" t="str">
         <x:v>task_prompt</x:v>
       </x:c>
-      <x:c r="F1" s="80" t="str">
+      <x:c r="F1" s="3" t="str">
         <x:v>success_criteria</x:v>
       </x:c>
-      <x:c r="G1" s="80" t="str">
+      <x:c r="G1" s="3" t="str">
         <x:v>critical_failure</x:v>
       </x:c>
-      <x:c r="H1" s="80" t="str">
+      <x:c r="H1" s="3" t="str">
         <x:v>primary_metrics</x:v>
       </x:c>
-      <x:c r="I1" s="80" t="str">
+      <x:c r="I1" s="3" t="str">
         <x:v>desktop</x:v>
       </x:c>
-      <x:c r="J1" s="80" t="str">
+      <x:c r="J1" s="3" t="str">
         <x:v>narrow</x:v>
       </x:c>
-      <x:c r="K1" s="80" t="str">
+      <x:c r="K1" s="3" t="str">
         <x:v>notes</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="84" t="str">
+    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="A2" s="3" t="str">
         <x:v>UX-01</x:v>
       </x:c>
-      <x:c r="B2" s="84" t="str">
+      <x:c r="B2" s="3" t="str">
         <x:v>対局開始</x:v>
       </x:c>
-      <x:c r="C2" s="84" t="str">
+      <x:c r="C2" s="3" t="str">
         <x:v>対局条件を設定して開始する</x:v>
       </x:c>
-      <x:c r="D2" s="84" t="str">
+      <x:c r="D2" s="3" t="str">
         <x:v>初期局面・先手あなた・後手AI初級</x:v>
       </x:c>
-      <x:c r="E2" s="84" t="str">
+      <x:c r="E2" s="3" t="str">
         <x:v>あなたが先手でAI初級との新しい対局を始めてください</x:v>
       </x:c>
-      <x:c r="F2" s="84" t="str">
+      <x:c r="F2" s="3" t="str">
         <x:v>0手目の先手番で対局操作が可能になる</x:v>
       </x:c>
-      <x:c r="G2" s="84" t="str">
+      <x:c r="G2" s="3" t="str">
         <x:v>意図しない設定または棋譜消失に気付かず開始する</x:v>
       </x:c>
-      <x:c r="H2" s="84" t="str">
+      <x:c r="H2" s="3" t="str">
         <x:v>elapsed_seconds|click_count|scroll_count|error_count</x:v>
       </x:c>
-      <x:c r="I2" s="84" t="str">
+      <x:c r="I2" s="3" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="J2" s="84" t="str">
+      <x:c r="J2" s="3" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="K2" s="84" t="str">
+      <x:c r="K2" s="3" t="str">
         <x:v>新規対局確認が出ない初期状態を使用</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="84" t="str">
+    <x:row r="3" ht="42" customHeight="1">
+      <x:c r="A3" s="3" t="str">
         <x:v>UX-02</x:v>
       </x:c>
-      <x:c r="B3" s="84" t="str">
+      <x:c r="B3" s="3" t="str">
         <x:v>着手と棋譜確認</x:v>
       </x:c>
-      <x:c r="C3" s="84" t="str">
+      <x:c r="C3" s="3" t="str">
         <x:v>一手指してAI応手と棋譜を確認する</x:v>
       </x:c>
-      <x:c r="D3" s="84" t="str">
+      <x:c r="D3" s="3" t="str">
         <x:v>UX-01完了直後</x:v>
       </x:c>
-      <x:c r="E3" s="84" t="str">
+      <x:c r="E3" s="3" t="str">
         <x:v>７七の歩を７六へ動かしAIの応手後に棋譜を確認してください</x:v>
       </x:c>
-      <x:c r="F3" s="84" t="str">
+      <x:c r="F3" s="3" t="str">
         <x:v>2手以上の棋譜と現在手数を確認できる</x:v>
       </x:c>
-      <x:c r="G3" s="84" t="str">
+      <x:c r="G3" s="3" t="str">
         <x:v>非合法手・別の駒・AI応手前の誤認</x:v>
       </x:c>
-      <x:c r="H3" s="84" t="str">
+      <x:c r="H3" s="3" t="str">
         <x:v>elapsed_seconds|click_count|scroll_count|error_count</x:v>
       </x:c>
-      <x:c r="I3" s="84" t="str">
+      <x:c r="I3" s="3" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="J3" s="84" t="str">
+      <x:c r="J3" s="3" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="K3" s="84" t="str">
+      <x:c r="K3" s="3" t="str">
         <x:v>AI応手は毎回異なる可能性あり</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="84" t="str">
+    <x:row r="4" ht="42" customHeight="1">
+      <x:c r="A4" s="3" t="str">
         <x:v>UX-03</x:v>
       </x:c>
-      <x:c r="B4" s="84" t="str">
+      <x:c r="B4" s="3" t="str">
         <x:v>対局から解析</x:v>
       </x:c>
-      <x:c r="C4" s="84" t="str">
+      <x:c r="C4" s="3" t="str">
         <x:v>現在の棋譜を解析して最善手を確認する</x:v>
       </x:c>
-      <x:c r="D4" s="84" t="str">
+      <x:c r="D4" s="3" t="str">
         <x:v>2手以上の棋譜あり・最終局面</x:v>
       </x:c>
-      <x:c r="E4" s="84" t="str">
+      <x:c r="E4" s="3" t="str">
         <x:v>この対局をAIで解析し現在局面の最善手を確認してください</x:v>
       </x:c>
-      <x:c r="F4" s="84" t="str">
+      <x:c r="F4" s="3" t="str">
         <x:v>解析完了後に現在局面の最善手または合法手なしを確認できる</x:v>
       </x:c>
-      <x:c r="G4" s="84" t="str">
+      <x:c r="G4" s="3" t="str">
         <x:v>解析開始を発見できない・別局面の結果を現在局面と誤認する</x:v>
       </x:c>
-      <x:c r="H4" s="84" t="str">
+      <x:c r="H4" s="3" t="str">
         <x:v>elapsed_seconds|click_count|scroll_count|error_count</x:v>
       </x:c>
-      <x:c r="I4" s="84" t="str">
+      <x:c r="I4" s="3" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="J4" s="84" t="str">
+      <x:c r="J4" s="3" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="K4" s="84" t="str">
+      <x:c r="K4" s="3" t="str">
         <x:v>解析完了待ちを時間に含む</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="84" t="str">
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="3" t="str">
         <x:v>UX-04</x:v>
       </x:c>
-      <x:c r="B5" s="84" t="str">
+      <x:c r="B5" s="3" t="str">
         <x:v>KIF解析</x:v>
       </x:c>
-      <x:c r="C5" s="84" t="str">
+      <x:c r="C5" s="3" t="str">
         <x:v>外部棋譜を読み込み特定局面を調べる</x:v>
       </x:c>
-      <x:c r="D5" s="84" t="str">
+      <x:c r="D5" s="3" t="str">
         <x:v>初期局面</x:v>
       </x:c>
-      <x:c r="E5" s="84" t="str">
+      <x:c r="E5" s="3" t="str">
         <x:v>テストKIFを読み込み3手目へ移動して評価を確認してください</x:v>
       </x:c>
-      <x:c r="F5" s="84" t="str">
+      <x:c r="F5" s="3" t="str">
         <x:v>5手KIFの3手目と対応する解析結果を確認できる</x:v>
       </x:c>
-      <x:c r="G5" s="84" t="str">
+      <x:c r="G5" s="3" t="str">
         <x:v>KIF読込失敗・局面を誤認・元棋譜を意図せず失う</x:v>
       </x:c>
-      <x:c r="H5" s="84" t="str">
+      <x:c r="H5" s="3" t="str">
         <x:v>elapsed_seconds|click_count|scroll_count|recovery_count</x:v>
       </x:c>
-      <x:c r="I5" s="84" t="str">
+      <x:c r="I5" s="3" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="J5" s="84" t="str">
+      <x:c r="J5" s="3" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="K5" s="84" t="str">
+      <x:c r="K5" s="3" t="str">
         <x:v>既存QA仕様の正常系KIFを使用</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="84" t="str">
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="3" t="str">
         <x:v>UX-05</x:v>
       </x:c>
-      <x:c r="B6" s="84" t="str">
+      <x:c r="B6" s="3" t="str">
         <x:v>保存と共有</x:v>
       </x:c>
-      <x:c r="C6" s="84" t="str">
+      <x:c r="C6" s="3" t="str">
         <x:v>解析後の棋譜を持ち出す</x:v>
       </x:c>
-      <x:c r="D6" s="84" t="str">
+      <x:c r="D6" s="3" t="str">
         <x:v>解析済みの5手KIF・3手目</x:v>
       </x:c>
-      <x:c r="E6" s="84" t="str">
+      <x:c r="E6" s="3" t="str">
         <x:v>この棋譜を保存できる場所と共有できる操作を示しURL共有を実行してください</x:v>
       </x:c>
-      <x:c r="F6" s="84" t="str">
+      <x:c r="F6" s="3" t="str">
         <x:v>保存操作とURL共有操作を発見し共有完了を確認できる</x:v>
       </x:c>
-      <x:c r="G6" s="84" t="str">
+      <x:c r="G6" s="3" t="str">
         <x:v>誤って新規対局・投了・棋譜破棄を実行する</x:v>
       </x:c>
-      <x:c r="H6" s="84" t="str">
+      <x:c r="H6" s="3" t="str">
         <x:v>elapsed_seconds|click_count|scroll_count|error_count</x:v>
       </x:c>
-      <x:c r="I6" s="84" t="str">
+      <x:c r="I6" s="3" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="J6" s="84" t="str">
+      <x:c r="J6" s="3" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="K6" s="84" t="str">
+      <x:c r="K6" s="3" t="str">
         <x:v>ダウンロード実行は不要・URL共有のみ実行</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re32ddc6ba0724407"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7e6080bd3344431"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -919,771 +786,765 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="23" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="13" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="13" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="13" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="13" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="13" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="13" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="24" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="34" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="12" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="12" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="14" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="28" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="28" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="48" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="42" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="46" hidden="0" customWidth="1"/>
     <x:col min="21" max="21" width="18" hidden="0" customWidth="1"/>
-    <x:col min="22" max="22" width="48" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="52" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="80" t="str">
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="3" t="str">
         <x:v>run_id</x:v>
       </x:c>
-      <x:c r="B1" s="80" t="str">
+      <x:c r="B1" s="3" t="str">
         <x:v>record_type</x:v>
       </x:c>
-      <x:c r="C1" s="80" t="str">
+      <x:c r="C1" s="3" t="str">
         <x:v>scenario_id</x:v>
       </x:c>
-      <x:c r="D1" s="80" t="str">
+      <x:c r="D1" s="3" t="str">
         <x:v>variant</x:v>
       </x:c>
-      <x:c r="E1" s="80" t="str">
+      <x:c r="E1" s="3" t="str">
         <x:v>environment</x:v>
       </x:c>
-      <x:c r="F1" s="80" t="str">
+      <x:c r="F1" s="3" t="str">
         <x:v>viewport</x:v>
       </x:c>
-      <x:c r="G1" s="80" t="str">
+      <x:c r="G1" s="3" t="str">
         <x:v>test_date</x:v>
       </x:c>
-      <x:c r="H1" s="80" t="str">
+      <x:c r="H1" s="3" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I1" s="80" t="str">
+      <x:c r="I1" s="3" t="str">
         <x:v>method</x:v>
       </x:c>
-      <x:c r="J1" s="80" t="str">
+      <x:c r="J1" s="3" t="str">
         <x:v>status</x:v>
       </x:c>
-      <x:c r="K1" s="80" t="str">
+      <x:c r="K1" s="3" t="str">
         <x:v>elapsed_seconds</x:v>
       </x:c>
-      <x:c r="L1" s="80" t="str">
+      <x:c r="L1" s="3" t="str">
         <x:v>click_count</x:v>
       </x:c>
-      <x:c r="M1" s="80" t="str">
+      <x:c r="M1" s="3" t="str">
         <x:v>scroll_count</x:v>
       </x:c>
-      <x:c r="N1" s="80" t="str">
+      <x:c r="N1" s="3" t="str">
         <x:v>key_count</x:v>
       </x:c>
-      <x:c r="O1" s="80" t="str">
+      <x:c r="O1" s="3" t="str">
         <x:v>error_count</x:v>
       </x:c>
-      <x:c r="P1" s="80" t="str">
+      <x:c r="P1" s="3" t="str">
         <x:v>recovery_count</x:v>
       </x:c>
-      <x:c r="Q1" s="80" t="str">
+      <x:c r="Q1" s="3" t="str">
         <x:v>start_state</x:v>
       </x:c>
-      <x:c r="R1" s="80" t="str">
+      <x:c r="R1" s="3" t="str">
         <x:v>end_state</x:v>
       </x:c>
-      <x:c r="S1" s="80" t="str">
+      <x:c r="S1" s="3" t="str">
         <x:v>observation</x:v>
       </x:c>
-      <x:c r="T1" s="80" t="str">
+      <x:c r="T1" s="3" t="str">
         <x:v>evidence</x:v>
       </x:c>
-      <x:c r="U1" s="80" t="str">
+      <x:c r="U1" s="3" t="str">
         <x:v>human_participant_id</x:v>
       </x:c>
-      <x:c r="V1" s="80" t="str">
+      <x:c r="V1" s="3" t="str">
         <x:v>limitations</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="84" t="str">
+    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="A2" s="3" t="str">
         <x:v>BASELINE-001</x:v>
       </x:c>
-      <x:c r="B2" s="84" t="str">
+      <x:c r="B2" s="3" t="str">
         <x:v>Computer Use benchmark</x:v>
       </x:c>
-      <x:c r="C2" s="84" t="str">
+      <x:c r="C2" s="3" t="str">
         <x:v>UX-01</x:v>
       </x:c>
-      <x:c r="D2" s="84" t="str">
+      <x:c r="D2" s="3" t="str">
         <x:v>BASE</x:v>
       </x:c>
-      <x:c r="E2" s="84" t="str">
+      <x:c r="E2" s="3" t="str">
         <x:v>ENV-01 Desktop</x:v>
       </x:c>
-      <x:c r="F2" s="84" t="str">
+      <x:c r="F2" s="3" t="str">
         <x:v>Desktop Chrome</x:v>
       </x:c>
-      <x:c r="G2" s="86" t="str">
+      <x:c r="G2" s="4" t="str">
         <x:v>2026-07-21</x:v>
       </x:c>
-      <x:c r="H2" s="84" t="str">
+      <x:c r="H2" s="3" t="str">
         <x:v>Codex Computer Use</x:v>
       </x:c>
-      <x:c r="I2" s="84" t="str">
+      <x:c r="I2" s="3" t="str">
         <x:v>Single-call scripted visual benchmark</x:v>
       </x:c>
-      <x:c r="J2" s="84" t="str">
+      <x:c r="J2" s="3" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="K2" s="88" t="str">
+      <x:c r="K2" s="5" t="n">
         <x:v>0.465</x:v>
       </x:c>
-      <x:c r="L2" s="90" t="str">
+      <x:c r="L2" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M2" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O2" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P2" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q2" s="84" t="str">
+      <x:c r="M2" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N2" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O2" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P2" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q2" s="3" t="str">
         <x:v>初期局面</x:v>
       </x:c>
-      <x:c r="R2" s="84" t="str">
+      <x:c r="R2" s="3" t="str">
         <x:v>0手目の先手番</x:v>
       </x:c>
-      <x:c r="S2" s="84" t="str">
+      <x:c r="S2" s="3" t="str">
         <x:v>盤と対局カードが同じ表示範囲にあり新規対局へスクロールなしで到達</x:v>
       </x:c>
-      <x:c r="T2" s="84" t="str">
+      <x:c r="T2" s="3" t="str">
         <x:v>docs/ux/mode-separation/evidence/BASELINE-001/desktop-current-game.jpeg</x:v>
       </x:c>
-      <x:c r="U2" s="84" t="str"/>
-      <x:c r="V2" s="84" t="str">
+      <x:c r="U2" s="3"/>
+      <x:c r="V2" s="3" t="str">
         <x:v>操作者はラベルと正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="84" t="str">
+    <x:row r="3" ht="42" customHeight="1">
+      <x:c r="A3" s="3" t="str">
         <x:v>BASELINE-001</x:v>
       </x:c>
-      <x:c r="B3" s="84" t="str">
+      <x:c r="B3" s="3" t="str">
         <x:v>Computer Use benchmark</x:v>
       </x:c>
-      <x:c r="C3" s="84" t="str">
+      <x:c r="C3" s="3" t="str">
         <x:v>UX-02</x:v>
       </x:c>
-      <x:c r="D3" s="84" t="str">
+      <x:c r="D3" s="3" t="str">
         <x:v>BASE</x:v>
       </x:c>
-      <x:c r="E3" s="84" t="str">
+      <x:c r="E3" s="3" t="str">
         <x:v>ENV-01 Desktop</x:v>
       </x:c>
-      <x:c r="F3" s="84" t="str">
+      <x:c r="F3" s="3" t="str">
         <x:v>Desktop Chrome</x:v>
       </x:c>
-      <x:c r="G3" s="86" t="str">
+      <x:c r="G3" s="4" t="str">
         <x:v>2026-07-21</x:v>
       </x:c>
-      <x:c r="H3" s="84" t="str">
+      <x:c r="H3" s="3" t="str">
         <x:v>Codex Computer Use</x:v>
       </x:c>
-      <x:c r="I3" s="84" t="str">
+      <x:c r="I3" s="3" t="str">
         <x:v>Single-call scripted visual benchmark</x:v>
       </x:c>
-      <x:c r="J3" s="84" t="str">
+      <x:c r="J3" s="3" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="K3" s="88" t="str">
+      <x:c r="K3" s="5" t="n">
         <x:v>1.201</x:v>
       </x:c>
-      <x:c r="L3" s="90" t="str">
+      <x:c r="L3" s="6" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="M3" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O3" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P3" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q3" s="84" t="str">
+      <x:c r="M3" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N3" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O3" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P3" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q3" s="3" t="str">
         <x:v>0手目の先手番</x:v>
       </x:c>
-      <x:c r="R3" s="84" t="str">
+      <x:c r="R3" s="3" t="str">
         <x:v>AI応手後の2手目と棋譜</x:v>
       </x:c>
-      <x:c r="S3" s="84" t="str">
+      <x:c r="S3" s="3" t="str">
         <x:v>盤と棋譜を横並びで確認でき上下移動は不要</x:v>
       </x:c>
-      <x:c r="T3" s="84" t="str">
+      <x:c r="T3" s="3" t="str">
         <x:v>docs/ux/mode-separation/evidence/BASELINE-001/desktop-current-game.jpeg</x:v>
       </x:c>
-      <x:c r="U3" s="84" t="str"/>
-      <x:c r="V3" s="84" t="str">
+      <x:c r="U3" s="3"/>
+      <x:c r="V3" s="3" t="str">
         <x:v>操作者はラベルと正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="84" t="str">
+    <x:row r="4" ht="42" customHeight="1">
+      <x:c r="A4" s="3" t="str">
         <x:v>BASELINE-001</x:v>
       </x:c>
-      <x:c r="B4" s="84" t="str">
+      <x:c r="B4" s="3" t="str">
         <x:v>Computer Use benchmark</x:v>
       </x:c>
-      <x:c r="C4" s="84" t="str">
+      <x:c r="C4" s="3" t="str">
         <x:v>UX-03</x:v>
       </x:c>
-      <x:c r="D4" s="84" t="str">
+      <x:c r="D4" s="3" t="str">
         <x:v>BASE</x:v>
       </x:c>
-      <x:c r="E4" s="84" t="str">
+      <x:c r="E4" s="3" t="str">
         <x:v>ENV-01 Desktop</x:v>
       </x:c>
-      <x:c r="F4" s="84" t="str">
+      <x:c r="F4" s="3" t="str">
         <x:v>Desktop Chrome</x:v>
       </x:c>
-      <x:c r="G4" s="86" t="str">
+      <x:c r="G4" s="4" t="str">
         <x:v>2026-07-21</x:v>
       </x:c>
-      <x:c r="H4" s="84" t="str">
+      <x:c r="H4" s="3" t="str">
         <x:v>Codex Computer Use</x:v>
       </x:c>
-      <x:c r="I4" s="84" t="str">
+      <x:c r="I4" s="3" t="str">
         <x:v>Single-call scripted visual benchmark</x:v>
       </x:c>
-      <x:c r="J4" s="84" t="str">
+      <x:c r="J4" s="3" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="K4" s="88" t="str">
+      <x:c r="K4" s="5" t="n">
         <x:v>1.719</x:v>
       </x:c>
-      <x:c r="L4" s="90" t="str">
+      <x:c r="L4" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M4" s="90" t="str">
+      <x:c r="M4" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N4" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O4" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P4" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q4" s="84" t="str">
+      <x:c r="N4" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O4" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P4" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q4" s="3" t="str">
         <x:v>2手目の最終局面</x:v>
       </x:c>
-      <x:c r="R4" s="84" t="str">
+      <x:c r="R4" s="3" t="str">
         <x:v>現在局面の最善手と評価グラフ</x:v>
       </x:c>
-      <x:c r="S4" s="84" t="str">
+      <x:c r="S4" s="3" t="str">
         <x:v>解析ボタンは最初の表示範囲下端にあるが結果が下へ展開するため視覚確認に1回スクロール</x:v>
       </x:c>
-      <x:c r="T4" s="84" t="str">
+      <x:c r="T4" s="3" t="str">
         <x:v>docs/ux/mode-separation/evidence/BASELINE-001/desktop-analysis-result.jpeg</x:v>
       </x:c>
-      <x:c r="U4" s="84" t="str"/>
-      <x:c r="V4" s="84" t="str">
+      <x:c r="U4" s="3"/>
+      <x:c r="V4" s="3" t="str">
         <x:v>操作者はラベルと正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="84" t="str">
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="3" t="str">
         <x:v>BASELINE-001</x:v>
       </x:c>
-      <x:c r="B5" s="84" t="str">
+      <x:c r="B5" s="3" t="str">
         <x:v>Computer Use benchmark</x:v>
       </x:c>
-      <x:c r="C5" s="84" t="str">
+      <x:c r="C5" s="3" t="str">
         <x:v>UX-04</x:v>
       </x:c>
-      <x:c r="D5" s="84" t="str">
+      <x:c r="D5" s="3" t="str">
         <x:v>BASE</x:v>
       </x:c>
-      <x:c r="E5" s="84" t="str">
+      <x:c r="E5" s="3" t="str">
         <x:v>ENV-01 Desktop</x:v>
       </x:c>
-      <x:c r="F5" s="84" t="str">
+      <x:c r="F5" s="3" t="str">
         <x:v>Desktop Chrome</x:v>
       </x:c>
-      <x:c r="G5" s="86" t="str">
+      <x:c r="G5" s="4" t="str">
         <x:v>2026-07-21</x:v>
       </x:c>
-      <x:c r="H5" s="84" t="str">
+      <x:c r="H5" s="3" t="str">
         <x:v>Codex Computer Use</x:v>
       </x:c>
-      <x:c r="I5" s="84" t="str">
+      <x:c r="I5" s="3" t="str">
         <x:v>Single-call scripted visual benchmark</x:v>
       </x:c>
-      <x:c r="J5" s="84" t="str">
+      <x:c r="J5" s="3" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="K5" s="88" t="str">
+      <x:c r="K5" s="5" t="n">
         <x:v>4.567</x:v>
       </x:c>
-      <x:c r="L5" s="90" t="str">
+      <x:c r="L5" s="6" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="M5" s="90" t="str">
+      <x:c r="M5" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N5" s="90" t="str">
+      <x:c r="N5" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O5" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P5" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q5" s="84" t="str">
+      <x:c r="O5" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P5" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q5" s="3" t="str">
         <x:v>初期局面</x:v>
       </x:c>
-      <x:c r="R5" s="84" t="str">
+      <x:c r="R5" s="3" t="str">
         <x:v>5手KIFの3手目と解析結果</x:v>
       </x:c>
-      <x:c r="S5" s="84" t="str">
+      <x:c r="S5" s="3" t="str">
         <x:v>KIF読込で棋譜一覧が伸び解析カードが下へ移動するため3手目から解析へ1回スクロール</x:v>
       </x:c>
-      <x:c r="T5" s="84" t="str">
+      <x:c r="T5" s="3" t="str">
         <x:v>docs/ux/mode-separation/evidence/BASELINE-001/desktop-analysis-result.jpeg</x:v>
       </x:c>
-      <x:c r="U5" s="84" t="str"/>
-      <x:c r="V5" s="84" t="str">
+      <x:c r="U5" s="3"/>
+      <x:c r="V5" s="3" t="str">
         <x:v>操作者はラベルと正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="84" t="str">
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="3" t="str">
         <x:v>BASELINE-001</x:v>
       </x:c>
-      <x:c r="B6" s="84" t="str">
+      <x:c r="B6" s="3" t="str">
         <x:v>Computer Use benchmark</x:v>
       </x:c>
-      <x:c r="C6" s="84" t="str">
+      <x:c r="C6" s="3" t="str">
         <x:v>UX-05</x:v>
       </x:c>
-      <x:c r="D6" s="84" t="str">
+      <x:c r="D6" s="3" t="str">
         <x:v>BASE</x:v>
       </x:c>
-      <x:c r="E6" s="84" t="str">
+      <x:c r="E6" s="3" t="str">
         <x:v>ENV-01 Desktop</x:v>
       </x:c>
-      <x:c r="F6" s="84" t="str">
+      <x:c r="F6" s="3" t="str">
         <x:v>Desktop Chrome</x:v>
       </x:c>
-      <x:c r="G6" s="86" t="str">
+      <x:c r="G6" s="4" t="str">
         <x:v>2026-07-21</x:v>
       </x:c>
-      <x:c r="H6" s="84" t="str">
+      <x:c r="H6" s="3" t="str">
         <x:v>Codex Computer Use</x:v>
       </x:c>
-      <x:c r="I6" s="84" t="str">
+      <x:c r="I6" s="3" t="str">
         <x:v>Single-call scripted visual benchmark</x:v>
       </x:c>
-      <x:c r="J6" s="84" t="str">
+      <x:c r="J6" s="3" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="K6" s="88" t="str">
+      <x:c r="K6" s="5" t="n">
         <x:v>1.406</x:v>
       </x:c>
-      <x:c r="L6" s="90" t="str">
+      <x:c r="L6" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M6" s="90" t="str">
+      <x:c r="M6" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N6" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O6" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P6" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q6" s="84" t="str">
+      <x:c r="N6" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O6" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P6" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q6" s="3" t="str">
         <x:v>解析済み5手KIFの3手目</x:v>
       </x:c>
-      <x:c r="R6" s="84" t="str">
+      <x:c r="R6" s="3" t="str">
         <x:v>URL共有完了</x:v>
       </x:c>
-      <x:c r="S6" s="84" t="str">
+      <x:c r="S6" s="3" t="str">
         <x:v>解析結果から上にあるURL共有へ戻るため1回上方向スクロール</x:v>
       </x:c>
-      <x:c r="T6" s="84" t="str">
+      <x:c r="T6" s="3" t="str">
         <x:v>docs/ux/mode-separation/evidence/BASELINE-001/desktop-analysis-result.jpeg</x:v>
       </x:c>
-      <x:c r="U6" s="84" t="str"/>
-      <x:c r="V6" s="84" t="str">
+      <x:c r="U6" s="3"/>
+      <x:c r="V6" s="3" t="str">
         <x:v>操作者はラベルと正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="84" t="str">
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="3" t="str">
         <x:v>BASELINE-001</x:v>
       </x:c>
-      <x:c r="B7" s="84" t="str">
+      <x:c r="B7" s="3" t="str">
         <x:v>Computer Use benchmark</x:v>
       </x:c>
-      <x:c r="C7" s="84" t="str">
+      <x:c r="C7" s="3" t="str">
         <x:v>UX-01</x:v>
       </x:c>
-      <x:c r="D7" s="84" t="str">
+      <x:c r="D7" s="3" t="str">
         <x:v>BASE</x:v>
       </x:c>
-      <x:c r="E7" s="84" t="str">
+      <x:c r="E7" s="3" t="str">
         <x:v>ENV-02 Narrow</x:v>
       </x:c>
-      <x:c r="F7" s="84" t="str">
+      <x:c r="F7" s="3" t="str">
         <x:v>400x625</x:v>
       </x:c>
-      <x:c r="G7" s="86" t="str">
+      <x:c r="G7" s="4" t="str">
         <x:v>2026-07-21</x:v>
       </x:c>
-      <x:c r="H7" s="84" t="str">
+      <x:c r="H7" s="3" t="str">
         <x:v>Codex Computer Use</x:v>
       </x:c>
-      <x:c r="I7" s="84" t="str">
+      <x:c r="I7" s="3" t="str">
         <x:v>Single-call scripted visual benchmark</x:v>
       </x:c>
-      <x:c r="J7" s="84" t="str">
+      <x:c r="J7" s="3" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="K7" s="88" t="str">
+      <x:c r="K7" s="5" t="n">
         <x:v>2.649</x:v>
       </x:c>
-      <x:c r="L7" s="90" t="str">
+      <x:c r="L7" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M7" s="90" t="str">
+      <x:c r="M7" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N7" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O7" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P7" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q7" s="84" t="str">
+      <x:c r="N7" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O7" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P7" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q7" s="3" t="str">
         <x:v>初期局面</x:v>
       </x:c>
-      <x:c r="R7" s="84" t="str">
+      <x:c r="R7" s="3" t="str">
         <x:v>0手目の先手番</x:v>
       </x:c>
-      <x:c r="S7" s="84" t="str">
+      <x:c r="S7" s="3" t="str">
         <x:v>初期表示は盤が中心で新規対局ボタンへ到達するには1回下方向スクロール</x:v>
       </x:c>
-      <x:c r="T7" s="84" t="str">
+      <x:c r="T7" s="3" t="str">
         <x:v>docs/ux/mode-separation/evidence/BASELINE-001/mobile-initial.jpeg</x:v>
       </x:c>
-      <x:c r="U7" s="84" t="str"/>
-      <x:c r="V7" s="84" t="str">
+      <x:c r="U7" s="3"/>
+      <x:c r="V7" s="3" t="str">
         <x:v>操作者はラベルと正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="84" t="str">
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="3" t="str">
         <x:v>BASELINE-001</x:v>
       </x:c>
-      <x:c r="B8" s="84" t="str">
+      <x:c r="B8" s="3" t="str">
         <x:v>Computer Use benchmark</x:v>
       </x:c>
-      <x:c r="C8" s="84" t="str">
+      <x:c r="C8" s="3" t="str">
         <x:v>UX-02</x:v>
       </x:c>
-      <x:c r="D8" s="84" t="str">
+      <x:c r="D8" s="3" t="str">
         <x:v>BASE</x:v>
       </x:c>
-      <x:c r="E8" s="84" t="str">
+      <x:c r="E8" s="3" t="str">
         <x:v>ENV-02 Narrow</x:v>
       </x:c>
-      <x:c r="F8" s="84" t="str">
+      <x:c r="F8" s="3" t="str">
         <x:v>400x625</x:v>
       </x:c>
-      <x:c r="G8" s="86" t="str">
+      <x:c r="G8" s="4" t="str">
         <x:v>2026-07-21</x:v>
       </x:c>
-      <x:c r="H8" s="84" t="str">
+      <x:c r="H8" s="3" t="str">
         <x:v>Codex Computer Use</x:v>
       </x:c>
-      <x:c r="I8" s="84" t="str">
+      <x:c r="I8" s="3" t="str">
         <x:v>Single-call scripted visual benchmark</x:v>
       </x:c>
-      <x:c r="J8" s="84" t="str">
+      <x:c r="J8" s="3" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="K8" s="88" t="str">
+      <x:c r="K8" s="5" t="n">
         <x:v>4.264</x:v>
       </x:c>
-      <x:c r="L8" s="90" t="str">
+      <x:c r="L8" s="6" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="M8" s="90" t="str">
+      <x:c r="M8" s="6" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N8" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O8" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P8" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q8" s="84" t="str">
+      <x:c r="N8" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O8" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P8" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q8" s="3" t="str">
         <x:v>0手目の対局カード</x:v>
       </x:c>
-      <x:c r="R8" s="84" t="str">
+      <x:c r="R8" s="3" t="str">
         <x:v>AI応手後の2手目と棋譜</x:v>
       </x:c>
-      <x:c r="S8" s="84" t="str">
+      <x:c r="S8" s="3" t="str">
         <x:v>対局カードから盤へ戻り着手後に棋譜へ進むため上下2回のスクロール</x:v>
       </x:c>
-      <x:c r="T8" s="84" t="str">
+      <x:c r="T8" s="3" t="str">
         <x:v>docs/ux/mode-separation/evidence/BASELINE-001/mobile-initial.jpeg</x:v>
       </x:c>
-      <x:c r="U8" s="84" t="str"/>
-      <x:c r="V8" s="84" t="str">
+      <x:c r="U8" s="3"/>
+      <x:c r="V8" s="3" t="str">
         <x:v>操作者はラベルと正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="84" t="str">
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="3" t="str">
         <x:v>BASELINE-001</x:v>
       </x:c>
-      <x:c r="B9" s="84" t="str">
+      <x:c r="B9" s="3" t="str">
         <x:v>Computer Use benchmark</x:v>
       </x:c>
-      <x:c r="C9" s="84" t="str">
+      <x:c r="C9" s="3" t="str">
         <x:v>UX-03</x:v>
       </x:c>
-      <x:c r="D9" s="84" t="str">
+      <x:c r="D9" s="3" t="str">
         <x:v>BASE</x:v>
       </x:c>
-      <x:c r="E9" s="84" t="str">
+      <x:c r="E9" s="3" t="str">
         <x:v>ENV-02 Narrow</x:v>
       </x:c>
-      <x:c r="F9" s="84" t="str">
+      <x:c r="F9" s="3" t="str">
         <x:v>400x625</x:v>
       </x:c>
-      <x:c r="G9" s="86" t="str">
+      <x:c r="G9" s="4" t="str">
         <x:v>2026-07-21</x:v>
       </x:c>
-      <x:c r="H9" s="84" t="str">
+      <x:c r="H9" s="3" t="str">
         <x:v>Codex Computer Use</x:v>
       </x:c>
-      <x:c r="I9" s="84" t="str">
+      <x:c r="I9" s="3" t="str">
         <x:v>Single-call scripted visual benchmark</x:v>
       </x:c>
-      <x:c r="J9" s="84" t="str">
+      <x:c r="J9" s="3" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="K9" s="88" t="str">
-        <x:v>3.160</x:v>
-      </x:c>
-      <x:c r="L9" s="90" t="str">
+      <x:c r="K9" s="5" t="n">
+        <x:v>3.16</x:v>
+      </x:c>
+      <x:c r="L9" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M9" s="90" t="str">
+      <x:c r="M9" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N9" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O9" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P9" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q9" s="84" t="str">
+      <x:c r="N9" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O9" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P9" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q9" s="3" t="str">
         <x:v>2手目の棋譜カード</x:v>
       </x:c>
-      <x:c r="R9" s="84" t="str">
+      <x:c r="R9" s="3" t="str">
         <x:v>現在局面の最善手と評価グラフ</x:v>
       </x:c>
-      <x:c r="S9" s="84" t="str">
+      <x:c r="S9" s="3" t="str">
         <x:v>解析ボタンは棋譜カード付近にあるが展開結果を見るためさらに1回下方向スクロール</x:v>
       </x:c>
-      <x:c r="T9" s="84" t="str">
+      <x:c r="T9" s="3" t="str">
         <x:v>docs/ux/mode-separation/evidence/BASELINE-001/mobile-analysis-result.jpeg</x:v>
       </x:c>
-      <x:c r="U9" s="84" t="str"/>
-      <x:c r="V9" s="84" t="str">
+      <x:c r="U9" s="3"/>
+      <x:c r="V9" s="3" t="str">
         <x:v>操作者はラベルと正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="84" t="str">
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="3" t="str">
         <x:v>BASELINE-001</x:v>
       </x:c>
-      <x:c r="B10" s="84" t="str">
+      <x:c r="B10" s="3" t="str">
         <x:v>Computer Use benchmark</x:v>
       </x:c>
-      <x:c r="C10" s="84" t="str">
+      <x:c r="C10" s="3" t="str">
         <x:v>UX-04</x:v>
       </x:c>
-      <x:c r="D10" s="84" t="str">
+      <x:c r="D10" s="3" t="str">
         <x:v>BASE</x:v>
       </x:c>
-      <x:c r="E10" s="84" t="str">
+      <x:c r="E10" s="3" t="str">
         <x:v>ENV-02 Narrow</x:v>
       </x:c>
-      <x:c r="F10" s="84" t="str">
+      <x:c r="F10" s="3" t="str">
         <x:v>400x625</x:v>
       </x:c>
-      <x:c r="G10" s="86" t="str">
+      <x:c r="G10" s="4" t="str">
         <x:v>2026-07-21</x:v>
       </x:c>
-      <x:c r="H10" s="84" t="str">
+      <x:c r="H10" s="3" t="str">
         <x:v>Codex Computer Use</x:v>
       </x:c>
-      <x:c r="I10" s="84" t="str">
+      <x:c r="I10" s="3" t="str">
         <x:v>Single-call scripted visual benchmark</x:v>
       </x:c>
-      <x:c r="J10" s="84" t="str">
+      <x:c r="J10" s="3" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="K10" s="88" t="str">
+      <x:c r="K10" s="5" t="n">
         <x:v>9.646</x:v>
       </x:c>
-      <x:c r="L10" s="90" t="str">
+      <x:c r="L10" s="6" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="M10" s="90" t="str">
+      <x:c r="M10" s="6" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N10" s="90" t="str">
+      <x:c r="N10" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O10" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P10" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q10" s="84" t="str">
+      <x:c r="O10" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P10" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q10" s="3" t="str">
         <x:v>初期局面</x:v>
       </x:c>
-      <x:c r="R10" s="84" t="str">
+      <x:c r="R10" s="3" t="str">
         <x:v>5手KIFの3手目と解析結果</x:v>
       </x:c>
-      <x:c r="S10" s="84" t="str">
+      <x:c r="S10" s="3" t="str">
         <x:v>KIF読込への移動と解析カードへの移動で合計2回スクロール</x:v>
       </x:c>
-      <x:c r="T10" s="84" t="str">
+      <x:c r="T10" s="3" t="str">
         <x:v>docs/ux/mode-separation/evidence/BASELINE-001/mobile-analysis-result.jpeg</x:v>
       </x:c>
-      <x:c r="U10" s="84" t="str"/>
-      <x:c r="V10" s="84" t="str">
+      <x:c r="U10" s="3"/>
+      <x:c r="V10" s="3" t="str">
         <x:v>操作者はラベルと正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="84" t="str">
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="3" t="str">
         <x:v>BASELINE-001</x:v>
       </x:c>
-      <x:c r="B11" s="84" t="str">
+      <x:c r="B11" s="3" t="str">
         <x:v>Computer Use benchmark</x:v>
       </x:c>
-      <x:c r="C11" s="84" t="str">
+      <x:c r="C11" s="3" t="str">
         <x:v>UX-05</x:v>
       </x:c>
-      <x:c r="D11" s="84" t="str">
+      <x:c r="D11" s="3" t="str">
         <x:v>BASE</x:v>
       </x:c>
-      <x:c r="E11" s="84" t="str">
+      <x:c r="E11" s="3" t="str">
         <x:v>ENV-02 Narrow</x:v>
       </x:c>
-      <x:c r="F11" s="84" t="str">
+      <x:c r="F11" s="3" t="str">
         <x:v>400x625</x:v>
       </x:c>
-      <x:c r="G11" s="86" t="str">
+      <x:c r="G11" s="4" t="str">
         <x:v>2026-07-21</x:v>
       </x:c>
-      <x:c r="H11" s="84" t="str">
+      <x:c r="H11" s="3" t="str">
         <x:v>Codex Computer Use</x:v>
       </x:c>
-      <x:c r="I11" s="84" t="str">
+      <x:c r="I11" s="3" t="str">
         <x:v>Single-call scripted visual benchmark</x:v>
       </x:c>
-      <x:c r="J11" s="84" t="str">
+      <x:c r="J11" s="3" t="str">
         <x:v>Pass</x:v>
       </x:c>
-      <x:c r="K11" s="88" t="str">
+      <x:c r="K11" s="5" t="n">
         <x:v>2.217</x:v>
       </x:c>
-      <x:c r="L11" s="90" t="str">
+      <x:c r="L11" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M11" s="90" t="str">
+      <x:c r="M11" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N11" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O11" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P11" s="90" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q11" s="84" t="str">
+      <x:c r="N11" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O11" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P11" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q11" s="3" t="str">
         <x:v>解析済み5手KIFの3手目</x:v>
       </x:c>
-      <x:c r="R11" s="84" t="str">
+      <x:c r="R11" s="3" t="str">
         <x:v>URL共有完了</x:v>
       </x:c>
-      <x:c r="S11" s="84" t="str">
+      <x:c r="S11" s="3" t="str">
         <x:v>解析結果の下側から棋譜カード内のURL共有へ1回上方向スクロール</x:v>
       </x:c>
-      <x:c r="T11" s="84" t="str">
+      <x:c r="T11" s="3" t="str">
         <x:v>docs/ux/mode-separation/evidence/BASELINE-001/mobile-analysis-result.jpeg</x:v>
       </x:c>
-      <x:c r="U11" s="84" t="str"/>
-      <x:c r="V11" s="84" t="str">
+      <x:c r="U11" s="3"/>
+      <x:c r="V11" s="3" t="str">
         <x:v>操作者はラベルと正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="J2:J1000">
+  <x:conditionalFormatting sqref="J2:J11">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Pass"/>
-    <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Fail"/>
   </x:conditionalFormatting>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="J2:J1000">
-      <x:formula1>"Not Run,Pass,Fail,Blocked"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b15c5f1658c4151"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd71547be1fd44f17"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1693,104 +1554,2085 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="18" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="18" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="36" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="36" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="36" hidden="0" customWidth="1"/>
-    <x:col min="22" max="22" width="36" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="34" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="12" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="12" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="14" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="28" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="28" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="48" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="50" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="18" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="56" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="80" t="str">
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="3" t="str">
         <x:v>run_id</x:v>
       </x:c>
-      <x:c r="B1" s="80" t="str">
+      <x:c r="B1" s="3" t="str">
         <x:v>record_type</x:v>
       </x:c>
-      <x:c r="C1" s="80" t="str">
+      <x:c r="C1" s="3" t="str">
         <x:v>scenario_id</x:v>
       </x:c>
-      <x:c r="D1" s="80" t="str">
+      <x:c r="D1" s="3" t="str">
         <x:v>variant</x:v>
       </x:c>
-      <x:c r="E1" s="80" t="str">
+      <x:c r="E1" s="3" t="str">
         <x:v>environment</x:v>
       </x:c>
-      <x:c r="F1" s="80" t="str">
+      <x:c r="F1" s="3" t="str">
         <x:v>viewport</x:v>
       </x:c>
-      <x:c r="G1" s="80" t="str">
+      <x:c r="G1" s="3" t="str">
         <x:v>test_date</x:v>
       </x:c>
-      <x:c r="H1" s="80" t="str">
+      <x:c r="H1" s="3" t="str">
         <x:v>operator</x:v>
       </x:c>
-      <x:c r="I1" s="80" t="str">
+      <x:c r="I1" s="3" t="str">
         <x:v>method</x:v>
       </x:c>
-      <x:c r="J1" s="80" t="str">
+      <x:c r="J1" s="3" t="str">
         <x:v>status</x:v>
       </x:c>
-      <x:c r="K1" s="80" t="str">
+      <x:c r="K1" s="3" t="str">
         <x:v>elapsed_seconds</x:v>
       </x:c>
-      <x:c r="L1" s="80" t="str">
+      <x:c r="L1" s="3" t="str">
         <x:v>click_count</x:v>
       </x:c>
-      <x:c r="M1" s="80" t="str">
+      <x:c r="M1" s="3" t="str">
         <x:v>scroll_count</x:v>
       </x:c>
-      <x:c r="N1" s="80" t="str">
+      <x:c r="N1" s="3" t="str">
         <x:v>key_count</x:v>
       </x:c>
-      <x:c r="O1" s="80" t="str">
+      <x:c r="O1" s="3" t="str">
         <x:v>error_count</x:v>
       </x:c>
-      <x:c r="P1" s="80" t="str">
+      <x:c r="P1" s="3" t="str">
         <x:v>recovery_count</x:v>
       </x:c>
-      <x:c r="Q1" s="80" t="str">
+      <x:c r="Q1" s="3" t="str">
         <x:v>start_state</x:v>
       </x:c>
-      <x:c r="R1" s="80" t="str">
+      <x:c r="R1" s="3" t="str">
         <x:v>end_state</x:v>
       </x:c>
-      <x:c r="S1" s="80" t="str">
+      <x:c r="S1" s="3" t="str">
         <x:v>observation</x:v>
       </x:c>
-      <x:c r="T1" s="80" t="str">
+      <x:c r="T1" s="3" t="str">
         <x:v>evidence</x:v>
       </x:c>
-      <x:c r="U1" s="80" t="str">
+      <x:c r="U1" s="3" t="str">
         <x:v>human_participant_id</x:v>
       </x:c>
-      <x:c r="V1" s="80" t="str">
+      <x:c r="V1" s="3" t="str">
         <x:v>limitations</x:v>
       </x:c>
     </x:row>
+    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="A2" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B2" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C2" s="3" t="str">
+        <x:v>UX-01</x:v>
+      </x:c>
+      <x:c r="D2" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="E2" s="3" t="str">
+        <x:v>ENV-01 Desktop</x:v>
+      </x:c>
+      <x:c r="F2" s="3" t="str">
+        <x:v>Desktop Chrome</x:v>
+      </x:c>
+      <x:c r="G2" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H2" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I2" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J2" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K2" s="5" t="n">
+        <x:v>0.566</x:v>
+      </x:c>
+      <x:c r="L2" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M2" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N2" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O2" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P2" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q2" s="3" t="str">
+        <x:v>初期局面・対局開始前</x:v>
+      </x:c>
+      <x:c r="R2" s="3" t="str">
+        <x:v>0手目の先手番</x:v>
+      </x:c>
+      <x:c r="S2" s="3" t="str">
+        <x:v>対局モード内の主要CTAから開始。盤と操作パネルを同時に確認</x:v>
+      </x:c>
+      <x:c r="T2" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/desktop-A-mode-analysis.png</x:v>
+      </x:c>
+      <x:c r="U2" s="3"/>
+      <x:c r="V2" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="42" customHeight="1">
+      <x:c r="A3" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="str">
+        <x:v>UX-02</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="str">
+        <x:v>ENV-01 Desktop</x:v>
+      </x:c>
+      <x:c r="F3" s="3" t="str">
+        <x:v>Desktop Chrome</x:v>
+      </x:c>
+      <x:c r="G3" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H3" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I3" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J3" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K3" s="5" t="n">
+        <x:v>1.146</x:v>
+      </x:c>
+      <x:c r="L3" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M3" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N3" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O3" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P3" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q3" s="3" t="str">
+        <x:v>0手目の先手番</x:v>
+      </x:c>
+      <x:c r="R3" s="3" t="str">
+        <x:v>AI応手後の2手目と棋譜</x:v>
+      </x:c>
+      <x:c r="S3" s="3" t="str">
+        <x:v>盤で着手後、同じ表示範囲の棋譜にAI応手まで反映</x:v>
+      </x:c>
+      <x:c r="T3" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/desktop-A-mode-analysis.png</x:v>
+      </x:c>
+      <x:c r="U3" s="3"/>
+      <x:c r="V3" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="42" customHeight="1">
+      <x:c r="A4" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="str">
+        <x:v>UX-03</x:v>
+      </x:c>
+      <x:c r="D4" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="E4" s="3" t="str">
+        <x:v>ENV-01 Desktop</x:v>
+      </x:c>
+      <x:c r="F4" s="3" t="str">
+        <x:v>Desktop Chrome</x:v>
+      </x:c>
+      <x:c r="G4" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H4" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I4" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J4" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K4" s="5" t="n">
+        <x:v>1.54</x:v>
+      </x:c>
+      <x:c r="L4" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M4" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N4" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O4" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P4" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q4" s="3" t="str">
+        <x:v>2手目の最終局面</x:v>
+      </x:c>
+      <x:c r="R4" s="3" t="str">
+        <x:v>現在局面の最善手と評価グラフ</x:v>
+      </x:c>
+      <x:c r="S4" s="3" t="str">
+        <x:v>解析モードへ切り替えて開始。局面と棋譜は保持</x:v>
+      </x:c>
+      <x:c r="T4" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/desktop-A-mode-analysis.png</x:v>
+      </x:c>
+      <x:c r="U4" s="3"/>
+      <x:c r="V4" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="42" customHeight="1">
+      <x:c r="A5" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C5" s="3" t="str">
+        <x:v>UX-04</x:v>
+      </x:c>
+      <x:c r="D5" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="E5" s="3" t="str">
+        <x:v>ENV-01 Desktop</x:v>
+      </x:c>
+      <x:c r="F5" s="3" t="str">
+        <x:v>Desktop Chrome</x:v>
+      </x:c>
+      <x:c r="G5" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H5" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I5" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J5" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K5" s="5" t="n">
+        <x:v>4.036</x:v>
+      </x:c>
+      <x:c r="L5" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M5" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N5" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O5" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P5" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q5" s="3" t="str">
+        <x:v>初期局面</x:v>
+      </x:c>
+      <x:c r="R5" s="3" t="str">
+        <x:v>5手KIFの3手目と解析結果</x:v>
+      </x:c>
+      <x:c r="S5" s="3" t="str">
+        <x:v>共通KIFを読み込み3手目へ移動。モード切替後も局面を保持</x:v>
+      </x:c>
+      <x:c r="T5" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/desktop-A-mode-analysis.png</x:v>
+      </x:c>
+      <x:c r="U5" s="3"/>
+      <x:c r="V5" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B6" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C6" s="3" t="str">
+        <x:v>UX-05</x:v>
+      </x:c>
+      <x:c r="D6" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="E6" s="3" t="str">
+        <x:v>ENV-01 Desktop</x:v>
+      </x:c>
+      <x:c r="F6" s="3" t="str">
+        <x:v>Desktop Chrome</x:v>
+      </x:c>
+      <x:c r="G6" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H6" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I6" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J6" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K6" s="5" t="n">
+        <x:v>0.789</x:v>
+      </x:c>
+      <x:c r="L6" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M6" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O6" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P6" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q6" s="3" t="str">
+        <x:v>解析済み5手KIFの3手目</x:v>
+      </x:c>
+      <x:c r="R6" s="3" t="str">
+        <x:v>URL共有完了</x:v>
+      </x:c>
+      <x:c r="S6" s="3" t="str">
+        <x:v>解析モードにも共通棋譜操作が残り、保存と共有へ直接到達</x:v>
+      </x:c>
+      <x:c r="T6" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/desktop-A-mode-analysis.png</x:v>
+      </x:c>
+      <x:c r="U6" s="3"/>
+      <x:c r="V6" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>UX-01</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="str">
+        <x:v>ENV-02 Narrow</x:v>
+      </x:c>
+      <x:c r="F7" s="3" t="str">
+        <x:v>400x625</x:v>
+      </x:c>
+      <x:c r="G7" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H7" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I7" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J7" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K7" s="5" t="n">
+        <x:v>3.122</x:v>
+      </x:c>
+      <x:c r="L7" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M7" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O7" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P7" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q7" s="3" t="str">
+        <x:v>初期局面・対局開始前</x:v>
+      </x:c>
+      <x:c r="R7" s="3" t="str">
+        <x:v>0手目の先手番</x:v>
+      </x:c>
+      <x:c r="S7" s="3" t="str">
+        <x:v>盤中心の初期表示から対局カードへ1回スクロールして開始</x:v>
+      </x:c>
+      <x:c r="T7" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/mobile-A-mode-analysis.png</x:v>
+      </x:c>
+      <x:c r="U7" s="3"/>
+      <x:c r="V7" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>UX-02</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="str">
+        <x:v>ENV-02 Narrow</x:v>
+      </x:c>
+      <x:c r="F8" s="3" t="str">
+        <x:v>400x625</x:v>
+      </x:c>
+      <x:c r="G8" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H8" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I8" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J8" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K8" s="5" t="n">
+        <x:v>4.988</x:v>
+      </x:c>
+      <x:c r="L8" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M8" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N8" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O8" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P8" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q8" s="3" t="str">
+        <x:v>0手目の先手番</x:v>
+      </x:c>
+      <x:c r="R8" s="3" t="str">
+        <x:v>AI応手後の2手目と棋譜</x:v>
+      </x:c>
+      <x:c r="S8" s="3" t="str">
+        <x:v>対局カードから盤へ戻り、着手後に棋譜へ移動するため上下2回</x:v>
+      </x:c>
+      <x:c r="T8" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/mobile-A-mode-analysis.png</x:v>
+      </x:c>
+      <x:c r="U8" s="3"/>
+      <x:c r="V8" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="str">
+        <x:v>UX-03</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="str">
+        <x:v>ENV-02 Narrow</x:v>
+      </x:c>
+      <x:c r="F9" s="3" t="str">
+        <x:v>400x625</x:v>
+      </x:c>
+      <x:c r="G9" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H9" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I9" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J9" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K9" s="5" t="n">
+        <x:v>4.549</x:v>
+      </x:c>
+      <x:c r="L9" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M9" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N9" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O9" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P9" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q9" s="3" t="str">
+        <x:v>2手目の最終局面</x:v>
+      </x:c>
+      <x:c r="R9" s="3" t="str">
+        <x:v>現在局面の最善手と評価グラフ</x:v>
+      </x:c>
+      <x:c r="S9" s="3" t="str">
+        <x:v>固定ドックで解析へ切り替えた後、解析CTAへ1回上方向スクロール</x:v>
+      </x:c>
+      <x:c r="T9" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/mobile-A-mode-analysis.png</x:v>
+      </x:c>
+      <x:c r="U9" s="3"/>
+      <x:c r="V9" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="str">
+        <x:v>UX-04</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="E10" s="3" t="str">
+        <x:v>ENV-02 Narrow</x:v>
+      </x:c>
+      <x:c r="F10" s="3" t="str">
+        <x:v>400x625</x:v>
+      </x:c>
+      <x:c r="G10" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H10" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I10" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J10" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K10" s="5" t="n">
+        <x:v>9.265</x:v>
+      </x:c>
+      <x:c r="L10" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M10" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N10" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O10" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P10" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q10" s="3" t="str">
+        <x:v>初期局面</x:v>
+      </x:c>
+      <x:c r="R10" s="3" t="str">
+        <x:v>5手KIFの3手目と解析結果</x:v>
+      </x:c>
+      <x:c r="S10" s="3" t="str">
+        <x:v>KIF操作領域へ下移動し、モード切替後の解析CTAへ上移動</x:v>
+      </x:c>
+      <x:c r="T10" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/mobile-A-mode-analysis.png</x:v>
+      </x:c>
+      <x:c r="U10" s="3"/>
+      <x:c r="V10" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B11" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="str">
+        <x:v>UX-05</x:v>
+      </x:c>
+      <x:c r="D11" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="E11" s="3" t="str">
+        <x:v>ENV-02 Narrow</x:v>
+      </x:c>
+      <x:c r="F11" s="3" t="str">
+        <x:v>400x625</x:v>
+      </x:c>
+      <x:c r="G11" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H11" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I11" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J11" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K11" s="5" t="n">
+        <x:v>3.038</x:v>
+      </x:c>
+      <x:c r="L11" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M11" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N11" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O11" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P11" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q11" s="3" t="str">
+        <x:v>解析済み5手KIFの3手目</x:v>
+      </x:c>
+      <x:c r="R11" s="3" t="str">
+        <x:v>URL共有完了</x:v>
+      </x:c>
+      <x:c r="S11" s="3" t="str">
+        <x:v>解析結果から共通棋譜操作へ1回下方向スクロールして共有</x:v>
+      </x:c>
+      <x:c r="T11" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/mobile-A-mode-analysis.png</x:v>
+      </x:c>
+      <x:c r="U11" s="3"/>
+      <x:c r="V11" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B12" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C12" s="3" t="str">
+        <x:v>UX-01</x:v>
+      </x:c>
+      <x:c r="D12" s="3" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="E12" s="3" t="str">
+        <x:v>ENV-01 Desktop</x:v>
+      </x:c>
+      <x:c r="F12" s="3" t="str">
+        <x:v>Desktop Chrome</x:v>
+      </x:c>
+      <x:c r="G12" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H12" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I12" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J12" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K12" s="5" t="n">
+        <x:v>0.566</x:v>
+      </x:c>
+      <x:c r="L12" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M12" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N12" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O12" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P12" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q12" s="3" t="str">
+        <x:v>初期局面・対局開始前</x:v>
+      </x:c>
+      <x:c r="R12" s="3" t="str">
+        <x:v>0手目の先手番</x:v>
+      </x:c>
+      <x:c r="S12" s="3" t="str">
+        <x:v>対局を基本表示にしたまま主要CTAから開始</x:v>
+      </x:c>
+      <x:c r="T12" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/desktop-B-sheet-analysis.png</x:v>
+      </x:c>
+      <x:c r="U12" s="3"/>
+      <x:c r="V12" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B13" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="str">
+        <x:v>UX-02</x:v>
+      </x:c>
+      <x:c r="D13" s="3" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="E13" s="3" t="str">
+        <x:v>ENV-01 Desktop</x:v>
+      </x:c>
+      <x:c r="F13" s="3" t="str">
+        <x:v>Desktop Chrome</x:v>
+      </x:c>
+      <x:c r="G13" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H13" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I13" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J13" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K13" s="5" t="n">
+        <x:v>1.042</x:v>
+      </x:c>
+      <x:c r="L13" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M13" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O13" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P13" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q13" s="3" t="str">
+        <x:v>0手目の先手番</x:v>
+      </x:c>
+      <x:c r="R13" s="3" t="str">
+        <x:v>AI応手後の2手目と棋譜</x:v>
+      </x:c>
+      <x:c r="S13" s="3" t="str">
+        <x:v>盤と棋譜を常時表示した状態でAI応手まで確認</x:v>
+      </x:c>
+      <x:c r="T13" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/desktop-B-sheet-analysis.png</x:v>
+      </x:c>
+      <x:c r="U13" s="3"/>
+      <x:c r="V13" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B14" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C14" s="3" t="str">
+        <x:v>UX-03</x:v>
+      </x:c>
+      <x:c r="D14" s="3" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="E14" s="3" t="str">
+        <x:v>ENV-01 Desktop</x:v>
+      </x:c>
+      <x:c r="F14" s="3" t="str">
+        <x:v>Desktop Chrome</x:v>
+      </x:c>
+      <x:c r="G14" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H14" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I14" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J14" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K14" s="5" t="n">
+        <x:v>1.319</x:v>
+      </x:c>
+      <x:c r="L14" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M14" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N14" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O14" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P14" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q14" s="3" t="str">
+        <x:v>2手目の最終局面</x:v>
+      </x:c>
+      <x:c r="R14" s="3" t="str">
+        <x:v>現在局面の最善手と評価グラフ</x:v>
+      </x:c>
+      <x:c r="S14" s="3" t="str">
+        <x:v>盤と棋譜を残した非モーダルシート内で解析結果を確認</x:v>
+      </x:c>
+      <x:c r="T14" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/desktop-B-sheet-analysis.png</x:v>
+      </x:c>
+      <x:c r="U14" s="3"/>
+      <x:c r="V14" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="42" customHeight="1">
+      <x:c r="A15" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B15" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C15" s="3" t="str">
+        <x:v>UX-04</x:v>
+      </x:c>
+      <x:c r="D15" s="3" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="E15" s="3" t="str">
+        <x:v>ENV-01 Desktop</x:v>
+      </x:c>
+      <x:c r="F15" s="3" t="str">
+        <x:v>Desktop Chrome</x:v>
+      </x:c>
+      <x:c r="G15" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H15" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I15" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J15" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K15" s="5" t="n">
+        <x:v>3.748</x:v>
+      </x:c>
+      <x:c r="L15" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M15" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N15" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O15" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P15" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q15" s="3" t="str">
+        <x:v>初期局面</x:v>
+      </x:c>
+      <x:c r="R15" s="3" t="str">
+        <x:v>5手KIFの3手目と解析結果</x:v>
+      </x:c>
+      <x:c r="S15" s="3" t="str">
+        <x:v>5手KIFの3手目を保持したまま解析シートを展開</x:v>
+      </x:c>
+      <x:c r="T15" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/desktop-B-sheet-analysis.png</x:v>
+      </x:c>
+      <x:c r="U15" s="3"/>
+      <x:c r="V15" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="42" customHeight="1">
+      <x:c r="A16" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B16" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C16" s="3" t="str">
+        <x:v>UX-05</x:v>
+      </x:c>
+      <x:c r="D16" s="3" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="E16" s="3" t="str">
+        <x:v>ENV-01 Desktop</x:v>
+      </x:c>
+      <x:c r="F16" s="3" t="str">
+        <x:v>Desktop Chrome</x:v>
+      </x:c>
+      <x:c r="G16" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H16" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I16" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J16" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K16" s="5" t="n">
+        <x:v>1.322</x:v>
+      </x:c>
+      <x:c r="L16" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M16" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N16" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O16" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P16" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q16" s="3" t="str">
+        <x:v>解析済み5手KIFの3手目</x:v>
+      </x:c>
+      <x:c r="R16" s="3" t="str">
+        <x:v>URL共有完了</x:v>
+      </x:c>
+      <x:c r="S16" s="3" t="str">
+        <x:v>保存・共有へ戻るには解析シートを閉じる1操作が必要</x:v>
+      </x:c>
+      <x:c r="T16" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/desktop-B-sheet-analysis.png</x:v>
+      </x:c>
+      <x:c r="U16" s="3"/>
+      <x:c r="V16" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="42" customHeight="1">
+      <x:c r="A17" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B17" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C17" s="3" t="str">
+        <x:v>UX-01</x:v>
+      </x:c>
+      <x:c r="D17" s="3" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="E17" s="3" t="str">
+        <x:v>ENV-02 Narrow</x:v>
+      </x:c>
+      <x:c r="F17" s="3" t="str">
+        <x:v>400x625</x:v>
+      </x:c>
+      <x:c r="G17" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H17" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I17" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J17" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K17" s="5" t="n">
+        <x:v>3.197</x:v>
+      </x:c>
+      <x:c r="L17" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M17" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N17" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O17" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P17" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q17" s="3" t="str">
+        <x:v>初期局面・対局開始前</x:v>
+      </x:c>
+      <x:c r="R17" s="3" t="str">
+        <x:v>0手目の先手番</x:v>
+      </x:c>
+      <x:c r="S17" s="3" t="str">
+        <x:v>盤中心の初期表示から対局カードへ1回スクロールして開始</x:v>
+      </x:c>
+      <x:c r="T17" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/mobile-B-sheet-analysis.png</x:v>
+      </x:c>
+      <x:c r="U17" s="3"/>
+      <x:c r="V17" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="42" customHeight="1">
+      <x:c r="A18" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B18" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C18" s="3" t="str">
+        <x:v>UX-02</x:v>
+      </x:c>
+      <x:c r="D18" s="3" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="E18" s="3" t="str">
+        <x:v>ENV-02 Narrow</x:v>
+      </x:c>
+      <x:c r="F18" s="3" t="str">
+        <x:v>400x625</x:v>
+      </x:c>
+      <x:c r="G18" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H18" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I18" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J18" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K18" s="5" t="n">
+        <x:v>4.355</x:v>
+      </x:c>
+      <x:c r="L18" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M18" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N18" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O18" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P18" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q18" s="3" t="str">
+        <x:v>0手目の先手番</x:v>
+      </x:c>
+      <x:c r="R18" s="3" t="str">
+        <x:v>AI応手後の2手目と棋譜</x:v>
+      </x:c>
+      <x:c r="S18" s="3" t="str">
+        <x:v>対局カードから盤へ戻り、着手後に棋譜へ移動するため上下2回</x:v>
+      </x:c>
+      <x:c r="T18" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/mobile-B-sheet-analysis.png</x:v>
+      </x:c>
+      <x:c r="U18" s="3"/>
+      <x:c r="V18" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="42" customHeight="1">
+      <x:c r="A19" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B19" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C19" s="3" t="str">
+        <x:v>UX-03</x:v>
+      </x:c>
+      <x:c r="D19" s="3" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="E19" s="3" t="str">
+        <x:v>ENV-02 Narrow</x:v>
+      </x:c>
+      <x:c r="F19" s="3" t="str">
+        <x:v>400x625</x:v>
+      </x:c>
+      <x:c r="G19" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H19" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I19" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J19" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K19" s="5" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="L19" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M19" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N19" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O19" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P19" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q19" s="3" t="str">
+        <x:v>2手目の最終局面</x:v>
+      </x:c>
+      <x:c r="R19" s="3" t="str">
+        <x:v>現在局面の最善手と評価グラフ</x:v>
+      </x:c>
+      <x:c r="S19" s="3" t="str">
+        <x:v>固定ドックからシートを開き、スクロールなしで解析開始と結果確認</x:v>
+      </x:c>
+      <x:c r="T19" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/mobile-B-sheet-analysis.png</x:v>
+      </x:c>
+      <x:c r="U19" s="3"/>
+      <x:c r="V19" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="42" customHeight="1">
+      <x:c r="A20" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B20" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C20" s="3" t="str">
+        <x:v>UX-04</x:v>
+      </x:c>
+      <x:c r="D20" s="3" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="E20" s="3" t="str">
+        <x:v>ENV-02 Narrow</x:v>
+      </x:c>
+      <x:c r="F20" s="3" t="str">
+        <x:v>400x625</x:v>
+      </x:c>
+      <x:c r="G20" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H20" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I20" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J20" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K20" s="5" t="n">
+        <x:v>7.651</x:v>
+      </x:c>
+      <x:c r="L20" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M20" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N20" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O20" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P20" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q20" s="3" t="str">
+        <x:v>初期局面</x:v>
+      </x:c>
+      <x:c r="R20" s="3" t="str">
+        <x:v>5手KIFの3手目と解析結果</x:v>
+      </x:c>
+      <x:c r="S20" s="3" t="str">
+        <x:v>KIF操作領域へ1回移動後、固定ドックとシート内で3手目を解析</x:v>
+      </x:c>
+      <x:c r="T20" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/mobile-B-sheet-analysis.png</x:v>
+      </x:c>
+      <x:c r="U20" s="3"/>
+      <x:c r="V20" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="42" customHeight="1">
+      <x:c r="A21" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B21" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C21" s="3" t="str">
+        <x:v>UX-05</x:v>
+      </x:c>
+      <x:c r="D21" s="3" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="E21" s="3" t="str">
+        <x:v>ENV-02 Narrow</x:v>
+      </x:c>
+      <x:c r="F21" s="3" t="str">
+        <x:v>400x625</x:v>
+      </x:c>
+      <x:c r="G21" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H21" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I21" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J21" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K21" s="5" t="n">
+        <x:v>3.53</x:v>
+      </x:c>
+      <x:c r="L21" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M21" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N21" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O21" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P21" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q21" s="3" t="str">
+        <x:v>解析済み5手KIFの3手目</x:v>
+      </x:c>
+      <x:c r="R21" s="3" t="str">
+        <x:v>URL共有完了</x:v>
+      </x:c>
+      <x:c r="S21" s="3" t="str">
+        <x:v>シートを閉じ、棋譜末尾の保存・共有へ1回下方向スクロール</x:v>
+      </x:c>
+      <x:c r="T21" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/mobile-B-sheet-analysis.png</x:v>
+      </x:c>
+      <x:c r="U21" s="3"/>
+      <x:c r="V21" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="42" customHeight="1">
+      <x:c r="A22" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B22" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C22" s="3" t="str">
+        <x:v>UX-01</x:v>
+      </x:c>
+      <x:c r="D22" s="3" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="E22" s="3" t="str">
+        <x:v>ENV-01 Desktop</x:v>
+      </x:c>
+      <x:c r="F22" s="3" t="str">
+        <x:v>Desktop Chrome</x:v>
+      </x:c>
+      <x:c r="G22" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H22" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I22" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J22" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K22" s="5" t="n">
+        <x:v>0.808</x:v>
+      </x:c>
+      <x:c r="L22" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M22" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N22" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O22" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P22" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q22" s="3" t="str">
+        <x:v>初期局面・対局開始前</x:v>
+      </x:c>
+      <x:c r="R22" s="3" t="str">
+        <x:v>0手目の先手番</x:v>
+      </x:c>
+      <x:c r="S22" s="3" t="str">
+        <x:v>次にすることカードの単一CTAから開始</x:v>
+      </x:c>
+      <x:c r="T22" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/desktop-D-hierarchy-analysis.png</x:v>
+      </x:c>
+      <x:c r="U22" s="3"/>
+      <x:c r="V22" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="42" customHeight="1">
+      <x:c r="A23" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B23" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C23" s="3" t="str">
+        <x:v>UX-02</x:v>
+      </x:c>
+      <x:c r="D23" s="3" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="E23" s="3" t="str">
+        <x:v>ENV-01 Desktop</x:v>
+      </x:c>
+      <x:c r="F23" s="3" t="str">
+        <x:v>Desktop Chrome</x:v>
+      </x:c>
+      <x:c r="G23" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H23" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I23" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J23" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K23" s="5" t="n">
+        <x:v>1.483</x:v>
+      </x:c>
+      <x:c r="L23" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M23" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N23" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O23" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P23" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q23" s="3" t="str">
+        <x:v>0手目の先手番</x:v>
+      </x:c>
+      <x:c r="R23" s="3" t="str">
+        <x:v>AI応手後の2手目と棋譜</x:v>
+      </x:c>
+      <x:c r="S23" s="3" t="str">
+        <x:v>盤で着手すると文脈CTAが解析へ更新され、棋譜にもAI応手を反映</x:v>
+      </x:c>
+      <x:c r="T23" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/desktop-D-hierarchy-analysis.png</x:v>
+      </x:c>
+      <x:c r="U23" s="3"/>
+      <x:c r="V23" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="42" customHeight="1">
+      <x:c r="A24" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B24" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C24" s="3" t="str">
+        <x:v>UX-03</x:v>
+      </x:c>
+      <x:c r="D24" s="3" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="E24" s="3" t="str">
+        <x:v>ENV-01 Desktop</x:v>
+      </x:c>
+      <x:c r="F24" s="3" t="str">
+        <x:v>Desktop Chrome</x:v>
+      </x:c>
+      <x:c r="G24" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H24" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I24" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J24" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K24" s="5" t="n">
+        <x:v>0.801</x:v>
+      </x:c>
+      <x:c r="L24" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M24" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N24" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O24" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P24" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q24" s="3" t="str">
+        <x:v>2手目の最終局面</x:v>
+      </x:c>
+      <x:c r="R24" s="3" t="str">
+        <x:v>現在局面の最善手と評価グラフ</x:v>
+      </x:c>
+      <x:c r="S24" s="3" t="str">
+        <x:v>情報階層の先頭にある文脈CTAから1操作で解析</x:v>
+      </x:c>
+      <x:c r="T24" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/desktop-D-hierarchy-analysis.png</x:v>
+      </x:c>
+      <x:c r="U24" s="3"/>
+      <x:c r="V24" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="42" customHeight="1">
+      <x:c r="A25" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B25" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C25" s="3" t="str">
+        <x:v>UX-04</x:v>
+      </x:c>
+      <x:c r="D25" s="3" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="E25" s="3" t="str">
+        <x:v>ENV-01 Desktop</x:v>
+      </x:c>
+      <x:c r="F25" s="3" t="str">
+        <x:v>Desktop Chrome</x:v>
+      </x:c>
+      <x:c r="G25" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H25" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I25" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J25" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K25" s="5" t="n">
+        <x:v>2.441</x:v>
+      </x:c>
+      <x:c r="L25" s="6" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M25" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N25" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O25" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P25" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q25" s="3" t="str">
+        <x:v>初期局面</x:v>
+      </x:c>
+      <x:c r="R25" s="3" t="str">
+        <x:v>5手KIFの3手目と解析結果</x:v>
+      </x:c>
+      <x:c r="S25" s="3" t="str">
+        <x:v>KIF読込後、開いた棋譜で3手目を選び文脈CTAから解析</x:v>
+      </x:c>
+      <x:c r="T25" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/desktop-D-hierarchy-analysis.png</x:v>
+      </x:c>
+      <x:c r="U25" s="3"/>
+      <x:c r="V25" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="42" customHeight="1">
+      <x:c r="A26" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B26" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C26" s="3" t="str">
+        <x:v>UX-05</x:v>
+      </x:c>
+      <x:c r="D26" s="3" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="E26" s="3" t="str">
+        <x:v>ENV-01 Desktop</x:v>
+      </x:c>
+      <x:c r="F26" s="3" t="str">
+        <x:v>Desktop Chrome</x:v>
+      </x:c>
+      <x:c r="G26" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H26" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I26" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J26" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K26" s="5" t="n">
+        <x:v>0.804</x:v>
+      </x:c>
+      <x:c r="L26" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M26" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N26" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O26" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P26" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q26" s="3" t="str">
+        <x:v>解析済み5手KIFの3手目</x:v>
+      </x:c>
+      <x:c r="R26" s="3" t="str">
+        <x:v>URL共有完了</x:v>
+      </x:c>
+      <x:c r="S26" s="3" t="str">
+        <x:v>解析完了後の主要CTAがURL共有へ変化。KIF保存は展開済み棋譜内に保持</x:v>
+      </x:c>
+      <x:c r="T26" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/desktop-D-hierarchy-analysis.png</x:v>
+      </x:c>
+      <x:c r="U26" s="3"/>
+      <x:c r="V26" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="42" customHeight="1">
+      <x:c r="A27" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B27" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C27" s="3" t="str">
+        <x:v>UX-01</x:v>
+      </x:c>
+      <x:c r="D27" s="3" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="E27" s="3" t="str">
+        <x:v>ENV-02 Narrow</x:v>
+      </x:c>
+      <x:c r="F27" s="3" t="str">
+        <x:v>400x625</x:v>
+      </x:c>
+      <x:c r="G27" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H27" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I27" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J27" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K27" s="5" t="n">
+        <x:v>1.896</x:v>
+      </x:c>
+      <x:c r="L27" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M27" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N27" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O27" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P27" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q27" s="3" t="str">
+        <x:v>初期局面・対局開始前</x:v>
+      </x:c>
+      <x:c r="R27" s="3" t="str">
+        <x:v>0手目の先手番</x:v>
+      </x:c>
+      <x:c r="S27" s="3" t="str">
+        <x:v>固定ドックの文脈CTAからスクロールなしで開始</x:v>
+      </x:c>
+      <x:c r="T27" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/mobile-D-analysis.png</x:v>
+      </x:c>
+      <x:c r="U27" s="3"/>
+      <x:c r="V27" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="42" customHeight="1">
+      <x:c r="A28" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B28" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C28" s="3" t="str">
+        <x:v>UX-02</x:v>
+      </x:c>
+      <x:c r="D28" s="3" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="E28" s="3" t="str">
+        <x:v>ENV-02 Narrow</x:v>
+      </x:c>
+      <x:c r="F28" s="3" t="str">
+        <x:v>400x625</x:v>
+      </x:c>
+      <x:c r="G28" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H28" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I28" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J28" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K28" s="5" t="n">
+        <x:v>3.07</x:v>
+      </x:c>
+      <x:c r="L28" s="6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M28" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N28" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O28" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P28" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q28" s="3" t="str">
+        <x:v>0手目の先手番</x:v>
+      </x:c>
+      <x:c r="R28" s="3" t="str">
+        <x:v>AI応手後の2手目と棋譜</x:v>
+      </x:c>
+      <x:c r="S28" s="3" t="str">
+        <x:v>盤上の着手後、展開済み棋譜の確認へ1回下方向スクロール</x:v>
+      </x:c>
+      <x:c r="T28" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/mobile-D-analysis.png</x:v>
+      </x:c>
+      <x:c r="U28" s="3"/>
+      <x:c r="V28" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="42" customHeight="1">
+      <x:c r="A29" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B29" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C29" s="3" t="str">
+        <x:v>UX-03</x:v>
+      </x:c>
+      <x:c r="D29" s="3" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="E29" s="3" t="str">
+        <x:v>ENV-02 Narrow</x:v>
+      </x:c>
+      <x:c r="F29" s="3" t="str">
+        <x:v>400x625</x:v>
+      </x:c>
+      <x:c r="G29" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H29" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I29" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J29" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K29" s="5" t="n">
+        <x:v>3.158</x:v>
+      </x:c>
+      <x:c r="L29" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M29" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N29" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O29" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P29" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q29" s="3" t="str">
+        <x:v>2手目の最終局面</x:v>
+      </x:c>
+      <x:c r="R29" s="3" t="str">
+        <x:v>現在局面の最善手と評価グラフ</x:v>
+      </x:c>
+      <x:c r="S29" s="3" t="str">
+        <x:v>固定ドックから1操作で解析し、挿入された結果へ1回上方向スクロール</x:v>
+      </x:c>
+      <x:c r="T29" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/mobile-D-analysis.png</x:v>
+      </x:c>
+      <x:c r="U29" s="3"/>
+      <x:c r="V29" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="42" customHeight="1">
+      <x:c r="A30" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B30" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C30" s="3" t="str">
+        <x:v>UX-04</x:v>
+      </x:c>
+      <x:c r="D30" s="3" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="E30" s="3" t="str">
+        <x:v>ENV-02 Narrow</x:v>
+      </x:c>
+      <x:c r="F30" s="3" t="str">
+        <x:v>400x625</x:v>
+      </x:c>
+      <x:c r="G30" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H30" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I30" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J30" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K30" s="5" t="n">
+        <x:v>6.681</x:v>
+      </x:c>
+      <x:c r="L30" s="6" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M30" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N30" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O30" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P30" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q30" s="3" t="str">
+        <x:v>初期局面</x:v>
+      </x:c>
+      <x:c r="R30" s="3" t="str">
+        <x:v>5手KIFの3手目と解析結果</x:v>
+      </x:c>
+      <x:c r="S30" s="3" t="str">
+        <x:v>KIF操作領域へ1回移動後、文脈CTAから3手目を解析</x:v>
+      </x:c>
+      <x:c r="T30" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/mobile-D-analysis.png</x:v>
+      </x:c>
+      <x:c r="U30" s="3"/>
+      <x:c r="V30" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="42" customHeight="1">
+      <x:c r="A31" s="3" t="str">
+        <x:v>PROTOTYPE-001</x:v>
+      </x:c>
+      <x:c r="B31" s="3" t="str">
+        <x:v>Computer Use benchmark</x:v>
+      </x:c>
+      <x:c r="C31" s="3" t="str">
+        <x:v>UX-05</x:v>
+      </x:c>
+      <x:c r="D31" s="3" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="E31" s="3" t="str">
+        <x:v>ENV-02 Narrow</x:v>
+      </x:c>
+      <x:c r="F31" s="3" t="str">
+        <x:v>400x625</x:v>
+      </x:c>
+      <x:c r="G31" s="4" t="str">
+        <x:v>2026-07-21</x:v>
+      </x:c>
+      <x:c r="H31" s="3" t="str">
+        <x:v>Codex Computer Use</x:v>
+      </x:c>
+      <x:c r="I31" s="3" t="str">
+        <x:v>Single-call scripted visual benchmark</x:v>
+      </x:c>
+      <x:c r="J31" s="3" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="K31" s="5" t="n">
+        <x:v>2.896</x:v>
+      </x:c>
+      <x:c r="L31" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M31" s="6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N31" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O31" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P31" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q31" s="3" t="str">
+        <x:v>解析済み5手KIFの3手目</x:v>
+      </x:c>
+      <x:c r="R31" s="3" t="str">
+        <x:v>URL共有完了</x:v>
+      </x:c>
+      <x:c r="S31" s="3" t="str">
+        <x:v>棋譜内のKIF保存を確認し、固定ドックのURL共有を実行</x:v>
+      </x:c>
+      <x:c r="T31" s="3" t="str">
+        <x:v>docs/ux/mode-separation/evidence/PROTOTYPE-001/mobile-D-analysis.png</x:v>
+      </x:c>
+      <x:c r="U31" s="3"/>
+      <x:c r="V31" s="3" t="str">
+        <x:v>正解経路を既知・経過時間はComputer Use待機を含む・人間の発見性は未評価・低忠実度プロトタイプ</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="J2:J1000">
-      <x:formula1>"Not Run,Pass,Fail,Blocked"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
+  <x:conditionalFormatting sqref="J2:J31">
+    <x:cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Pass"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4726e2d48a0a4869"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
@@ -1799,121 +3641,456 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="9" t="str">
         <x:v>対局／解析 情報分離 Discovery Tracker</x:v>
       </x:c>
-      <x:c r="B1" s="6"/>
-      <x:c r="C1" s="6"/>
-      <x:c r="D1" s="6"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="12" t="str">
+      <x:c r="B1" s="9"/>
+      <x:c r="C1" s="9"/>
+      <x:c r="D1" s="9"/>
+      <x:c r="E1" s="9"/>
+      <x:c r="F1" s="9"/>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="33" t="str">
         <x:v>指標</x:v>
       </x:c>
-      <x:c r="B3" s="12" t="str">
+      <x:c r="B3" s="33" t="str">
         <x:v>値</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="str">
+      <x:c r="C3" s="33" t="str">
         <x:v>説明</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="14" t="str">
+      <x:c r="D3" s="33"/>
+      <x:c r="E3" s="33"/>
+      <x:c r="F3" s="33"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="33" t="str">
         <x:v>ベースライン記録数</x:v>
       </x:c>
-      <x:c r="B4" s="20" t="n">
+      <x:c r="B4" s="34" t="n">
         <x:f>COUNTA('Baseline'!A2:A1000)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C4" s="14" t="str">
+      <x:c r="C4" s="33" t="str">
         <x:v>Computer Useと人間テストを含む行数</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="15" t="str">
+      <x:c r="D4" s="33"/>
+      <x:c r="E4" s="33"/>
+      <x:c r="F4" s="33"/>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="33" t="str">
         <x:v>Desktop 合計スクロール</x:v>
       </x:c>
-      <x:c r="B5" s="21" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:f>SUMIF('Baseline'!E2:E1000,"ENV-01 Desktop",'Baseline'!M2:M1000)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C5" s="15" t="str">
+      <x:c r="C5" s="33" t="str">
         <x:v>現行版5シナリオ</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="15" t="str">
+      <x:c r="D5" s="33"/>
+      <x:c r="E5" s="33"/>
+      <x:c r="F5" s="33"/>
+    </x:row>
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="33" t="str">
         <x:v>400px 合計スクロール</x:v>
       </x:c>
-      <x:c r="B6" s="21" t="n">
+      <x:c r="B6" s="34" t="n">
         <x:f>SUMIF('Baseline'!E2:E1000,"ENV-02 Narrow",'Baseline'!M2:M1000)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C6" s="15" t="str">
+      <x:c r="C6" s="33" t="str">
         <x:v>現行版5シナリオ</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="15" t="str">
+      <x:c r="D6" s="33"/>
+      <x:c r="E6" s="33"/>
+      <x:c r="F6" s="33"/>
+    </x:row>
+    <x:row r="7" ht="24" customHeight="1">
+      <x:c r="A7" s="33" t="str">
         <x:v>Desktop 自動操作秒</x:v>
       </x:c>
-      <x:c r="B7" s="24" t="n">
+      <x:c r="B7" s="35" t="n">
         <x:f>SUMIF('Baseline'!E2:E1000,"ENV-01 Desktop",'Baseline'!K2:K1000)</x:f>
         <x:v>9.358</x:v>
       </x:c>
-      <x:c r="C7" s="15" t="str">
+      <x:c r="C7" s="33" t="str">
         <x:v>同一方式内の比較専用</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="15" t="str">
+      <x:c r="D7" s="33"/>
+      <x:c r="E7" s="33"/>
+      <x:c r="F7" s="33"/>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="33" t="str">
         <x:v>400px 自動操作秒</x:v>
       </x:c>
-      <x:c r="B8" s="24" t="n">
+      <x:c r="B8" s="35" t="n">
         <x:f>SUMIF('Baseline'!E2:E1000,"ENV-02 Narrow",'Baseline'!K2:K1000)</x:f>
         <x:v>21.936</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="str">
+      <x:c r="C8" s="33" t="str">
         <x:v>同一方式内の比較専用</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="16" t="str">
+      <x:c r="D8" s="33"/>
+      <x:c r="E8" s="33"/>
+      <x:c r="F8" s="33"/>
+    </x:row>
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="33" t="str">
         <x:v>初見ユーザーセッション</x:v>
       </x:c>
-      <x:c r="B9" s="26" t="n">
-        <x:f>COUNTIF('Baseline'!B2:B1000,"Human usability test")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C9" s="16" t="str">
+      <x:c r="B9" s="34" t="n">
+        <x:f>COUNTIF('Baseline'!B2:B1000,"Human usability test")+COUNTIF('Prototype Results'!B2:B1000,"Human usability test")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C9" s="33" t="str">
         <x:v>目標は最低5セッション</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" ht="36" customHeight="1">
-      <x:c r="A11" s="56" t="str">
-        <x:v>注意: Computer Useの経過秒には自動操作基盤の待機時間が含まれます。人間のタスク時間と直接比較せず、同一方式・同一環境内の相対比較だけに使用してください。</x:v>
-      </x:c>
-      <x:c r="B11" s="57"/>
-      <x:c r="C11" s="57"/>
-      <x:c r="D11" s="58"/>
-    </x:row>
-    <x:row r="12" ht="36" customHeight="1">
-      <x:c r="A12" s="59"/>
-      <x:c r="B12" s="60"/>
-      <x:c r="C12" s="60"/>
-      <x:c r="D12" s="61"/>
+      <x:c r="D9" s="33"/>
+      <x:c r="E9" s="33"/>
+      <x:c r="F9" s="33"/>
+    </x:row>
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="33"/>
+      <x:c r="B10" s="33"/>
+      <x:c r="C10" s="33"/>
+      <x:c r="D10" s="33"/>
+      <x:c r="E10" s="33"/>
+      <x:c r="F10" s="33"/>
+    </x:row>
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="33" t="str">
+        <x:v>案</x:v>
+      </x:c>
+      <x:c r="B11" s="33" t="str">
+        <x:v>環境</x:v>
+      </x:c>
+      <x:c r="C11" s="33" t="str">
+        <x:v>完了</x:v>
+      </x:c>
+      <x:c r="D11" s="33" t="str">
+        <x:v>クリック</x:v>
+      </x:c>
+      <x:c r="E11" s="33" t="str">
+        <x:v>スクロール</x:v>
+      </x:c>
+      <x:c r="F11" s="33" t="str">
+        <x:v>自動操作秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="33" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="B12" s="33" t="str">
+        <x:v>ENV-01 Desktop</x:v>
+      </x:c>
+      <x:c r="C12" s="34" t="n">
+        <x:f>COUNTIFS('Prototype Results'!$D$2:$D$1000,A12,'Prototype Results'!$E$2:$E$1000,B12,'Prototype Results'!$J$2:$J$1000,"Pass")</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D12" s="34" t="n">
+        <x:f>SUMIFS('Prototype Results'!$L$2:$L$1000,'Prototype Results'!$D$2:$D$1000,A12,'Prototype Results'!$E$2:$E$1000,B12)</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E12" s="34" t="n">
+        <x:f>SUMIFS('Prototype Results'!$M$2:$M$1000,'Prototype Results'!$D$2:$D$1000,A12,'Prototype Results'!$E$2:$E$1000,B12)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F12" s="35" t="n">
+        <x:f>SUMIFS('Prototype Results'!$K$2:$K$1000,'Prototype Results'!$D$2:$D$1000,A12,'Prototype Results'!$E$2:$E$1000,B12)</x:f>
+        <x:v>8.077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13" s="33" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="B13" s="33" t="str">
+        <x:v>ENV-01 Desktop</x:v>
+      </x:c>
+      <x:c r="C13" s="34" t="n">
+        <x:f>COUNTIFS('Prototype Results'!$D$2:$D$1000,A13,'Prototype Results'!$E$2:$E$1000,B13,'Prototype Results'!$J$2:$J$1000,"Pass")</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D13" s="34" t="n">
+        <x:f>SUMIFS('Prototype Results'!$L$2:$L$1000,'Prototype Results'!$D$2:$D$1000,A13,'Prototype Results'!$E$2:$E$1000,B13)</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E13" s="34" t="n">
+        <x:f>SUMIFS('Prototype Results'!$M$2:$M$1000,'Prototype Results'!$D$2:$D$1000,A13,'Prototype Results'!$E$2:$E$1000,B13)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="35" t="n">
+        <x:f>SUMIFS('Prototype Results'!$K$2:$K$1000,'Prototype Results'!$D$2:$D$1000,A13,'Prototype Results'!$E$2:$E$1000,B13)</x:f>
+        <x:v>7.997000000000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="33" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="B14" s="33" t="str">
+        <x:v>ENV-01 Desktop</x:v>
+      </x:c>
+      <x:c r="C14" s="34" t="n">
+        <x:f>COUNTIFS('Prototype Results'!$D$2:$D$1000,A14,'Prototype Results'!$E$2:$E$1000,B14,'Prototype Results'!$J$2:$J$1000,"Pass")</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D14" s="34" t="n">
+        <x:f>SUMIFS('Prototype Results'!$L$2:$L$1000,'Prototype Results'!$D$2:$D$1000,A14,'Prototype Results'!$E$2:$E$1000,B14)</x:f>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E14" s="34" t="n">
+        <x:f>SUMIFS('Prototype Results'!$M$2:$M$1000,'Prototype Results'!$D$2:$D$1000,A14,'Prototype Results'!$E$2:$E$1000,B14)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F14" s="35" t="n">
+        <x:f>SUMIFS('Prototype Results'!$K$2:$K$1000,'Prototype Results'!$D$2:$D$1000,A14,'Prototype Results'!$E$2:$E$1000,B14)</x:f>
+        <x:v>6.337000000000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="33" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="B15" s="33" t="str">
+        <x:v>ENV-02 Narrow</x:v>
+      </x:c>
+      <x:c r="C15" s="34" t="n">
+        <x:f>COUNTIFS('Prototype Results'!$D$2:$D$1000,A15,'Prototype Results'!$E$2:$E$1000,B15,'Prototype Results'!$J$2:$J$1000,"Pass")</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D15" s="34" t="n">
+        <x:f>SUMIFS('Prototype Results'!$L$2:$L$1000,'Prototype Results'!$D$2:$D$1000,A15,'Prototype Results'!$E$2:$E$1000,B15)</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E15" s="34" t="n">
+        <x:f>SUMIFS('Prototype Results'!$M$2:$M$1000,'Prototype Results'!$D$2:$D$1000,A15,'Prototype Results'!$E$2:$E$1000,B15)</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F15" s="35" t="n">
+        <x:f>SUMIFS('Prototype Results'!$K$2:$K$1000,'Prototype Results'!$D$2:$D$1000,A15,'Prototype Results'!$E$2:$E$1000,B15)</x:f>
+        <x:v>24.962</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="24" customHeight="1">
+      <x:c r="A16" s="33" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="B16" s="33" t="str">
+        <x:v>ENV-02 Narrow</x:v>
+      </x:c>
+      <x:c r="C16" s="34" t="n">
+        <x:f>COUNTIFS('Prototype Results'!$D$2:$D$1000,A16,'Prototype Results'!$E$2:$E$1000,B16,'Prototype Results'!$J$2:$J$1000,"Pass")</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D16" s="34" t="n">
+        <x:f>SUMIFS('Prototype Results'!$L$2:$L$1000,'Prototype Results'!$D$2:$D$1000,A16,'Prototype Results'!$E$2:$E$1000,B16)</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E16" s="34" t="n">
+        <x:f>SUMIFS('Prototype Results'!$M$2:$M$1000,'Prototype Results'!$D$2:$D$1000,A16,'Prototype Results'!$E$2:$E$1000,B16)</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F16" s="35" t="n">
+        <x:f>SUMIFS('Prototype Results'!$K$2:$K$1000,'Prototype Results'!$D$2:$D$1000,A16,'Prototype Results'!$E$2:$E$1000,B16)</x:f>
+        <x:v>21.533</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="33" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="B17" s="33" t="str">
+        <x:v>ENV-02 Narrow</x:v>
+      </x:c>
+      <x:c r="C17" s="34" t="n">
+        <x:f>COUNTIFS('Prototype Results'!$D$2:$D$1000,A17,'Prototype Results'!$E$2:$E$1000,B17,'Prototype Results'!$J$2:$J$1000,"Pass")</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D17" s="34" t="n">
+        <x:f>SUMIFS('Prototype Results'!$L$2:$L$1000,'Prototype Results'!$D$2:$D$1000,A17,'Prototype Results'!$E$2:$E$1000,B17)</x:f>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E17" s="34" t="n">
+        <x:f>SUMIFS('Prototype Results'!$M$2:$M$1000,'Prototype Results'!$D$2:$D$1000,A17,'Prototype Results'!$E$2:$E$1000,B17)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F17" s="35" t="n">
+        <x:f>SUMIFS('Prototype Results'!$K$2:$K$1000,'Prototype Results'!$D$2:$D$1000,A17,'Prototype Results'!$E$2:$E$1000,B17)</x:f>
+        <x:v>17.701</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="33"/>
+      <x:c r="B18" s="33"/>
+      <x:c r="C18" s="33"/>
+      <x:c r="D18" s="33"/>
+      <x:c r="E18" s="33"/>
+      <x:c r="F18" s="33"/>
+    </x:row>
+    <x:row r="19" ht="24" customHeight="1">
+      <x:c r="A19" s="33"/>
+      <x:c r="B19" s="33"/>
+      <x:c r="C19" s="33"/>
+      <x:c r="D19" s="33"/>
+      <x:c r="E19" s="33"/>
+      <x:c r="F19" s="33"/>
+    </x:row>
+    <x:row r="20" ht="24" customHeight="1">
+      <x:c r="A20" s="9" t="str">
+        <x:v>400px 解析到達スクロール（UX-03 + UX-04）</x:v>
+      </x:c>
+      <x:c r="B20" s="9"/>
+      <x:c r="C20" s="9"/>
+      <x:c r="D20" s="9"/>
+      <x:c r="E20" s="33"/>
+      <x:c r="F20" s="33"/>
+    </x:row>
+    <x:row r="21" ht="24" customHeight="1">
+      <x:c r="A21" s="33" t="str">
+        <x:v>案</x:v>
+      </x:c>
+      <x:c r="B21" s="33" t="str">
+        <x:v>スクロール</x:v>
+      </x:c>
+      <x:c r="C21" s="33" t="str">
+        <x:v>BASE比削減</x:v>
+      </x:c>
+      <x:c r="D21" s="33" t="str">
+        <x:v>50%目標</x:v>
+      </x:c>
+      <x:c r="E21" s="33"/>
+      <x:c r="F21" s="33"/>
+    </x:row>
+    <x:row r="22" ht="24" customHeight="1">
+      <x:c r="A22" s="33" t="str">
+        <x:v>BASE</x:v>
+      </x:c>
+      <x:c r="B22" s="34" t="n">
+        <x:f>SUMIFS('Baseline'!M2:M1000,'Baseline'!E2:E1000,"ENV-02 Narrow",'Baseline'!C2:C1000,"UX-03")+SUMIFS('Baseline'!M2:M1000,'Baseline'!E2:E1000,"ENV-02 Narrow",'Baseline'!C2:C1000,"UX-04")</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C22" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D22" s="33" t="str">
+        <x:v>基準</x:v>
+      </x:c>
+      <x:c r="E22" s="33"/>
+      <x:c r="F22" s="33"/>
+    </x:row>
+    <x:row r="23" ht="24" customHeight="1">
+      <x:c r="A23" s="33" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="B23" s="34" t="n">
+        <x:f>SUMIFS('Prototype Results'!$M$2:$M$1000,'Prototype Results'!$D$2:$D$1000,A23,'Prototype Results'!$E$2:$E$1000,"ENV-02 Narrow",'Prototype Results'!$C$2:$C$1000,"UX-03")+SUMIFS('Prototype Results'!$M$2:$M$1000,'Prototype Results'!$D$2:$D$1000,A23,'Prototype Results'!$E$2:$E$1000,"ENV-02 Narrow",'Prototype Results'!$C$2:$C$1000,"UX-04")</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C23" s="36" t="n">
+        <x:f>1-B23/$B$22</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="33" t="str">
+        <x:f>IF(C23&gt;=0.5,"達成","未達")</x:f>
+        <x:v>未達</x:v>
+      </x:c>
+      <x:c r="E23" s="33"/>
+      <x:c r="F23" s="33"/>
+    </x:row>
+    <x:row r="24" ht="24" customHeight="1">
+      <x:c r="A24" s="33" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="B24" s="34" t="n">
+        <x:f>SUMIFS('Prototype Results'!$M$2:$M$1000,'Prototype Results'!$D$2:$D$1000,A24,'Prototype Results'!$E$2:$E$1000,"ENV-02 Narrow",'Prototype Results'!$C$2:$C$1000,"UX-03")+SUMIFS('Prototype Results'!$M$2:$M$1000,'Prototype Results'!$D$2:$D$1000,A24,'Prototype Results'!$E$2:$E$1000,"ENV-02 Narrow",'Prototype Results'!$C$2:$C$1000,"UX-04")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C24" s="36" t="n">
+        <x:f>1-B24/$B$22</x:f>
+        <x:v>0.6666666666666667</x:v>
+      </x:c>
+      <x:c r="D24" s="33" t="str">
+        <x:f>IF(C24&gt;=0.5,"達成","未達")</x:f>
+        <x:v>達成</x:v>
+      </x:c>
+      <x:c r="E24" s="33"/>
+      <x:c r="F24" s="33"/>
+    </x:row>
+    <x:row r="25" ht="24" customHeight="1">
+      <x:c r="A25" s="33" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="B25" s="34" t="n">
+        <x:f>SUMIFS('Prototype Results'!$M$2:$M$1000,'Prototype Results'!$D$2:$D$1000,A25,'Prototype Results'!$E$2:$E$1000,"ENV-02 Narrow",'Prototype Results'!$C$2:$C$1000,"UX-03")+SUMIFS('Prototype Results'!$M$2:$M$1000,'Prototype Results'!$D$2:$D$1000,A25,'Prototype Results'!$E$2:$E$1000,"ENV-02 Narrow",'Prototype Results'!$C$2:$C$1000,"UX-04")</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C25" s="36" t="n">
+        <x:f>1-B25/$B$22</x:f>
+        <x:v>0.33333333333333337</x:v>
+      </x:c>
+      <x:c r="D25" s="33" t="str">
+        <x:f>IF(C25&gt;=0.5,"達成","未達")</x:f>
+        <x:v>未達</x:v>
+      </x:c>
+      <x:c r="E25" s="33"/>
+      <x:c r="F25" s="33"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="33"/>
+      <x:c r="B26" s="33"/>
+      <x:c r="C26" s="33"/>
+      <x:c r="D26" s="33"/>
+      <x:c r="E26" s="33"/>
+      <x:c r="F26" s="33"/>
+    </x:row>
+    <x:row r="27" ht="32" customHeight="1">
+      <x:c r="A27" s="24" t="str">
+        <x:v>注意: Computer Useの経過秒には自動操作基盤の待機時間が含まれます。人間のタスク時間と直接比較せず、同一方式・同一環境内の相対比較だけに使用してください。初見ユーザーテストは未実施です。</x:v>
+      </x:c>
+      <x:c r="B27" s="25"/>
+      <x:c r="C27" s="25"/>
+      <x:c r="D27" s="25"/>
+      <x:c r="E27" s="25"/>
+      <x:c r="F27" s="26"/>
+    </x:row>
+    <x:row r="28" ht="32" customHeight="1">
+      <x:c r="A28" s="27"/>
+      <x:c r="B28" s="28"/>
+      <x:c r="C28" s="28"/>
+      <x:c r="D28" s="28"/>
+      <x:c r="E28" s="28"/>
+      <x:c r="F28" s="29"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:D1"/>
-    <x:mergeCell ref="A11:D12"/>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A20:D20"/>
+    <x:mergeCell ref="A27:F28"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="D23:D25">
+    <x:cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="達成"/>
+    <x:cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="未達"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="3">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R379992af9f3342e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0009761815664fff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b3e20b484a54367"/>
+  </x:tableParts>
 </x:worksheet>
 </file>